--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/09_Surcharge_50pct_1Trip.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/09_Surcharge_50pct_1Trip.xlsx
@@ -518,7 +518,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-04 18:51</t>
+          <t>2026-05-05 20:19</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/09_Surcharge_50pct_1Trip.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/09_Surcharge_50pct_1Trip.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Surcharge_50pct_1Trip" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Surcharge_50pct_1Trip" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Surcharge_50pct_1Trip'!$A$4:$L$44</definedName>
@@ -518,7 +518,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-05 20:19</t>
+          <t>2026-05-08 15:11</t>
         </is>
       </c>
     </row>
@@ -2104,10 +2104,10 @@
       </c>
       <c r="J40" s="9" t="n"/>
       <c r="K40" s="10" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="L40" s="10" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="41">
@@ -2146,10 +2146,10 @@
       </c>
       <c r="J41" s="6" t="n"/>
       <c r="K41" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="L41" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="42">

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/09_Surcharge_50pct_1Trip.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/09_Surcharge_50pct_1Trip.xlsx
@@ -518,7 +518,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 15:11</t>
+          <t>2026-05-08 15:54</t>
         </is>
       </c>
     </row>
@@ -634,10 +634,10 @@
       </c>
       <c r="J5" s="6" t="n"/>
       <c r="K5" s="7" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>3750</v>
+        <v>3412</v>
       </c>
     </row>
     <row r="6">
@@ -676,10 +676,10 @@
       </c>
       <c r="J6" s="9" t="n"/>
       <c r="K6" s="10" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="L6" s="10" t="n">
-        <v>3750</v>
+        <v>3412</v>
       </c>
     </row>
     <row r="7">
@@ -718,10 +718,10 @@
       </c>
       <c r="J7" s="6" t="n"/>
       <c r="K7" s="7" t="n">
-        <v>7500</v>
+        <v>7275</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>3750</v>
+        <v>3638</v>
       </c>
     </row>
     <row r="8">
@@ -760,10 +760,10 @@
       </c>
       <c r="J8" s="9" t="n"/>
       <c r="K8" s="10" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="L8" s="10" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="9">
@@ -802,10 +802,10 @@
       </c>
       <c r="J9" s="6" t="n"/>
       <c r="K9" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="10">
@@ -844,10 +844,10 @@
       </c>
       <c r="J10" s="9" t="n"/>
       <c r="K10" s="10" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="L10" s="10" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="11">
@@ -886,10 +886,10 @@
       </c>
       <c r="J11" s="6" t="n"/>
       <c r="K11" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="12">
@@ -928,10 +928,10 @@
       </c>
       <c r="J12" s="9" t="n"/>
       <c r="K12" s="10" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="L12" s="10" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="13">
@@ -970,10 +970,10 @@
       </c>
       <c r="J13" s="6" t="n"/>
       <c r="K13" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="14">
@@ -1012,10 +1012,10 @@
       </c>
       <c r="J14" s="9" t="n"/>
       <c r="K14" s="10" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="L14" s="10" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="15">
@@ -1054,10 +1054,10 @@
       </c>
       <c r="J15" s="6" t="n"/>
       <c r="K15" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="16">
@@ -1096,10 +1096,10 @@
       </c>
       <c r="J16" s="9" t="n"/>
       <c r="K16" s="10" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="L16" s="10" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="17">
@@ -1138,10 +1138,10 @@
       </c>
       <c r="J17" s="6" t="n"/>
       <c r="K17" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="18">
@@ -1180,10 +1180,10 @@
       </c>
       <c r="J18" s="9" t="n"/>
       <c r="K18" s="10" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="L18" s="10" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="19">
@@ -1222,10 +1222,10 @@
       </c>
       <c r="J19" s="6" t="n"/>
       <c r="K19" s="7" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="20">
@@ -1264,10 +1264,10 @@
       </c>
       <c r="J20" s="9" t="n"/>
       <c r="K20" s="10" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="L20" s="10" t="n">
-        <v>3750</v>
+        <v>3412</v>
       </c>
     </row>
     <row r="21">
@@ -1306,10 +1306,10 @@
       </c>
       <c r="J21" s="6" t="n"/>
       <c r="K21" s="7" t="n">
-        <v>7500</v>
+        <v>6825</v>
       </c>
       <c r="L21" s="7" t="n">
-        <v>3750</v>
+        <v>3412</v>
       </c>
     </row>
     <row r="22">
@@ -1348,10 +1348,10 @@
       </c>
       <c r="J22" s="9" t="n"/>
       <c r="K22" s="10" t="n">
-        <v>8000</v>
+        <v>7280</v>
       </c>
       <c r="L22" s="10" t="n">
-        <v>4000</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="23">
@@ -1390,10 +1390,10 @@
       </c>
       <c r="J23" s="6" t="n"/>
       <c r="K23" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="L23" s="7" t="n">
-        <v>3750</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="24">
@@ -1432,10 +1432,10 @@
       </c>
       <c r="J24" s="9" t="n"/>
       <c r="K24" s="10" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="L24" s="10" t="n">
-        <v>3750</v>
+        <v>3300</v>
       </c>
     </row>
     <row r="25">
@@ -1474,10 +1474,10 @@
       </c>
       <c r="J25" s="6" t="n"/>
       <c r="K25" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="L25" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="26">
@@ -1516,10 +1516,10 @@
       </c>
       <c r="J26" s="9" t="n"/>
       <c r="K26" s="10" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="L26" s="10" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="27">
@@ -1558,10 +1558,10 @@
       </c>
       <c r="J27" s="6" t="n"/>
       <c r="K27" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="L27" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="28">
@@ -1600,10 +1600,10 @@
       </c>
       <c r="J28" s="9" t="n"/>
       <c r="K28" s="10" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="L28" s="10" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="29">
@@ -1642,10 +1642,10 @@
       </c>
       <c r="J29" s="6" t="n"/>
       <c r="K29" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="L29" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="30">
@@ -1684,10 +1684,10 @@
       </c>
       <c r="J30" s="9" t="n"/>
       <c r="K30" s="10" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="L30" s="10" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="31">
@@ -1726,10 +1726,10 @@
       </c>
       <c r="J31" s="6" t="n"/>
       <c r="K31" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="L31" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="32">
@@ -1768,10 +1768,10 @@
       </c>
       <c r="J32" s="9" t="n"/>
       <c r="K32" s="10" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="L32" s="10" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="33">
@@ -1810,10 +1810,10 @@
       </c>
       <c r="J33" s="6" t="n"/>
       <c r="K33" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="L33" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="34">
@@ -1852,10 +1852,10 @@
       </c>
       <c r="J34" s="9" t="n"/>
       <c r="K34" s="10" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="L34" s="10" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="35">
@@ -1894,10 +1894,10 @@
       </c>
       <c r="J35" s="6" t="n"/>
       <c r="K35" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="L35" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="36">
@@ -1936,10 +1936,10 @@
       </c>
       <c r="J36" s="9" t="n"/>
       <c r="K36" s="10" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="L36" s="10" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="37">
@@ -1978,10 +1978,10 @@
       </c>
       <c r="J37" s="6" t="n"/>
       <c r="K37" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="L37" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="38">
@@ -2020,10 +2020,10 @@
       </c>
       <c r="J38" s="9" t="n"/>
       <c r="K38" s="10" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="L38" s="10" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="39">
@@ -2062,10 +2062,10 @@
       </c>
       <c r="J39" s="6" t="n"/>
       <c r="K39" s="7" t="n">
-        <v>7500</v>
+        <v>6500</v>
       </c>
       <c r="L39" s="7" t="n">
-        <v>3750</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="40">
@@ -2104,10 +2104,10 @@
       </c>
       <c r="J40" s="9" t="n"/>
       <c r="K40" s="10" t="n">
-        <v>6500</v>
+        <v>7378</v>
       </c>
       <c r="L40" s="10" t="n">
-        <v>3250</v>
+        <v>3689</v>
       </c>
     </row>
     <row r="41">
@@ -2146,10 +2146,10 @@
       </c>
       <c r="J41" s="6" t="n"/>
       <c r="K41" s="7" t="n">
-        <v>6500</v>
+        <v>7378</v>
       </c>
       <c r="L41" s="7" t="n">
-        <v>3250</v>
+        <v>3689</v>
       </c>
     </row>
     <row r="42">
@@ -2196,10 +2196,10 @@
         </is>
       </c>
       <c r="K42" s="10" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="L42" s="10" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="43">
@@ -2246,10 +2246,10 @@
         </is>
       </c>
       <c r="K43" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="L43" s="7" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
     </row>
     <row r="44">
@@ -2296,10 +2296,10 @@
         </is>
       </c>
       <c r="K44" s="10" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
       <c r="L44" s="10" t="n">
-        <v>7500</v>
+        <v>6600</v>
       </c>
     </row>
   </sheetData>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/09_Surcharge_50pct_1Trip.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/09_Surcharge_50pct_1Trip.xlsx
@@ -518,7 +518,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 15:54</t>
+          <t>2026-05-08 15:56</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/09_Surcharge_50pct_1Trip.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/09_Surcharge_50pct_1Trip.xlsx
@@ -518,7 +518,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 15:56</t>
+          <t>2026-05-08 16:35</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/09_Surcharge_50pct_1Trip.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/09_Surcharge_50pct_1Trip.xlsx
@@ -109,7 +109,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -118,7 +118,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -518,7 +518,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 16:35</t>
+          <t>2026-05-08 17:39</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/09_Surcharge_50pct_1Trip.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/09_Surcharge_50pct_1Trip.xlsx
@@ -518,7 +518,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 17:39</t>
+          <t>2026-05-08 18:09</t>
         </is>
       </c>
     </row>
@@ -634,10 +634,10 @@
       </c>
       <c r="J5" s="6" t="n"/>
       <c r="K5" s="7" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>3412</v>
+        <v>3425</v>
       </c>
     </row>
     <row r="6">
@@ -676,10 +676,10 @@
       </c>
       <c r="J6" s="9" t="n"/>
       <c r="K6" s="10" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="L6" s="10" t="n">
-        <v>3412</v>
+        <v>3425</v>
       </c>
     </row>
     <row r="7">
@@ -718,7 +718,7 @@
       </c>
       <c r="J7" s="6" t="n"/>
       <c r="K7" s="7" t="n">
-        <v>7275</v>
+        <v>7276.69</v>
       </c>
       <c r="L7" s="7" t="n">
         <v>3638</v>
@@ -760,10 +760,10 @@
       </c>
       <c r="J8" s="9" t="n"/>
       <c r="K8" s="10" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="L8" s="10" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
     </row>
     <row r="9">
@@ -802,10 +802,10 @@
       </c>
       <c r="J9" s="6" t="n"/>
       <c r="K9" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
     </row>
     <row r="10">
@@ -844,10 +844,10 @@
       </c>
       <c r="J10" s="9" t="n"/>
       <c r="K10" s="10" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="L10" s="10" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
     </row>
     <row r="11">
@@ -886,10 +886,10 @@
       </c>
       <c r="J11" s="6" t="n"/>
       <c r="K11" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
     </row>
     <row r="12">
@@ -928,10 +928,10 @@
       </c>
       <c r="J12" s="9" t="n"/>
       <c r="K12" s="10" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="L12" s="10" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
     </row>
     <row r="13">
@@ -970,10 +970,10 @@
       </c>
       <c r="J13" s="6" t="n"/>
       <c r="K13" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
     </row>
     <row r="14">
@@ -1012,10 +1012,10 @@
       </c>
       <c r="J14" s="9" t="n"/>
       <c r="K14" s="10" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="L14" s="10" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
     </row>
     <row r="15">
@@ -1054,10 +1054,10 @@
       </c>
       <c r="J15" s="6" t="n"/>
       <c r="K15" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
     </row>
     <row r="16">
@@ -1096,10 +1096,10 @@
       </c>
       <c r="J16" s="9" t="n"/>
       <c r="K16" s="10" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="L16" s="10" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
     </row>
     <row r="17">
@@ -1138,10 +1138,10 @@
       </c>
       <c r="J17" s="6" t="n"/>
       <c r="K17" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
     </row>
     <row r="18">
@@ -1180,10 +1180,10 @@
       </c>
       <c r="J18" s="9" t="n"/>
       <c r="K18" s="10" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="L18" s="10" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
     </row>
     <row r="19">
@@ -1222,10 +1222,10 @@
       </c>
       <c r="J19" s="6" t="n"/>
       <c r="K19" s="7" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
     </row>
     <row r="20">
@@ -1264,10 +1264,10 @@
       </c>
       <c r="J20" s="9" t="n"/>
       <c r="K20" s="10" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="L20" s="10" t="n">
-        <v>3412</v>
+        <v>3425</v>
       </c>
     </row>
     <row r="21">
@@ -1306,10 +1306,10 @@
       </c>
       <c r="J21" s="6" t="n"/>
       <c r="K21" s="7" t="n">
-        <v>6825</v>
+        <v>6849.81</v>
       </c>
       <c r="L21" s="7" t="n">
-        <v>3412</v>
+        <v>3425</v>
       </c>
     </row>
     <row r="22">
@@ -1348,10 +1348,10 @@
       </c>
       <c r="J22" s="9" t="n"/>
       <c r="K22" s="10" t="n">
-        <v>7280</v>
+        <v>7306.47</v>
       </c>
       <c r="L22" s="10" t="n">
-        <v>3640</v>
+        <v>3653</v>
       </c>
     </row>
     <row r="23">
@@ -1390,10 +1390,10 @@
       </c>
       <c r="J23" s="6" t="n"/>
       <c r="K23" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="L23" s="7" t="n">
-        <v>3300</v>
+        <v>3323</v>
       </c>
     </row>
     <row r="24">
@@ -1432,10 +1432,10 @@
       </c>
       <c r="J24" s="9" t="n"/>
       <c r="K24" s="10" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="L24" s="10" t="n">
-        <v>3300</v>
+        <v>3323</v>
       </c>
     </row>
     <row r="25">
@@ -1474,10 +1474,10 @@
       </c>
       <c r="J25" s="6" t="n"/>
       <c r="K25" s="7" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="L25" s="7" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
     </row>
     <row r="26">
@@ -1516,10 +1516,10 @@
       </c>
       <c r="J26" s="9" t="n"/>
       <c r="K26" s="10" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="L26" s="10" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
     </row>
     <row r="27">
@@ -1558,10 +1558,10 @@
       </c>
       <c r="J27" s="6" t="n"/>
       <c r="K27" s="7" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="L27" s="7" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
     </row>
     <row r="28">
@@ -1600,10 +1600,10 @@
       </c>
       <c r="J28" s="9" t="n"/>
       <c r="K28" s="10" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="L28" s="10" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
     </row>
     <row r="29">
@@ -1642,10 +1642,10 @@
       </c>
       <c r="J29" s="6" t="n"/>
       <c r="K29" s="7" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="L29" s="7" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
     </row>
     <row r="30">
@@ -1684,10 +1684,10 @@
       </c>
       <c r="J30" s="9" t="n"/>
       <c r="K30" s="10" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="L30" s="10" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
     </row>
     <row r="31">
@@ -1726,10 +1726,10 @@
       </c>
       <c r="J31" s="6" t="n"/>
       <c r="K31" s="7" t="n">
-        <v>6500</v>
+        <v>6546.17</v>
       </c>
       <c r="L31" s="7" t="n">
-        <v>3250</v>
+        <v>3273</v>
       </c>
     </row>
     <row r="32">
@@ -2104,10 +2104,10 @@
       </c>
       <c r="J40" s="9" t="n"/>
       <c r="K40" s="10" t="n">
-        <v>7378</v>
+        <v>7432.03</v>
       </c>
       <c r="L40" s="10" t="n">
-        <v>3689</v>
+        <v>3716</v>
       </c>
     </row>
     <row r="41">
@@ -2146,10 +2146,10 @@
       </c>
       <c r="J41" s="6" t="n"/>
       <c r="K41" s="7" t="n">
-        <v>7378</v>
+        <v>7432.03</v>
       </c>
       <c r="L41" s="7" t="n">
-        <v>3689</v>
+        <v>3716</v>
       </c>
     </row>
     <row r="42">
@@ -2196,10 +2196,10 @@
         </is>
       </c>
       <c r="K42" s="10" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="L42" s="10" t="n">
-        <v>6600</v>
+        <v>6645</v>
       </c>
     </row>
     <row r="43">
@@ -2246,10 +2246,10 @@
         </is>
       </c>
       <c r="K43" s="7" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="L43" s="7" t="n">
-        <v>6600</v>
+        <v>6645</v>
       </c>
     </row>
     <row r="44">
@@ -2296,10 +2296,10 @@
         </is>
       </c>
       <c r="K44" s="10" t="n">
-        <v>6600</v>
+        <v>6645.86</v>
       </c>
       <c r="L44" s="10" t="n">
-        <v>6600</v>
+        <v>6645</v>
       </c>
     </row>
   </sheetData>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/09_Surcharge_50pct_1Trip.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/09_Surcharge_50pct_1Trip.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Surcharge_50pct_1Trip" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Surcharge_50pct_1Trip'!$A$4:$L$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Surcharge_50pct_1Trip'!$A$4:$L$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:L42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -518,7 +518,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 18:09</t>
+          <t>2026-05-08 18:39</t>
         </is>
       </c>
     </row>
@@ -2070,21 +2070,21 @@
     </row>
     <row r="40">
       <c r="A40" s="8" t="n">
-        <v>46143</v>
+        <v>46133</v>
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-6802</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>midnight_full</t>
         </is>
       </c>
       <c r="E40" s="9" t="n">
@@ -2092,31 +2092,39 @@
       </c>
       <c r="F40" s="9" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G40" s="9" t="n"/>
-      <c r="H40" s="9" t="n"/>
+      <c r="H40" s="9" t="inlineStr">
+        <is>
+          <t>รอปลายทางข้ามคืน Dest_In→Dest_Out (20.96h); เต็ม 1 เที่ยว (เรทวัน Dest_In)</t>
+        </is>
+      </c>
       <c r="I40" s="9" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="J40" s="9" t="n"/>
+          <t>2026-04-21 16:38:59</t>
+        </is>
+      </c>
+      <c r="J40" s="9" t="inlineStr">
+        <is>
+          <t>2026-04-22 13:36:47</t>
+        </is>
+      </c>
       <c r="K40" s="10" t="n">
-        <v>7432.03</v>
+        <v>6645.86</v>
       </c>
       <c r="L40" s="10" t="n">
-        <v>3716</v>
+        <v>6645</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="n">
-        <v>46143</v>
+        <v>46133</v>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8681</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
@@ -2126,7 +2134,7 @@
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>midnight_full</t>
         </is>
       </c>
       <c r="E41" s="6" t="n">
@@ -2134,22 +2142,30 @@
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G41" s="6" t="n"/>
-      <c r="H41" s="6" t="n"/>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t>รอปลายทางข้ามคืน Dest_In→Dest_Out (21.30h); เต็ม 1 เที่ยว (เรทวัน Dest_In)</t>
+        </is>
+      </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="J41" s="6" t="n"/>
+          <t>2026-04-21 13:37:02</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>2026-04-22 10:55:11</t>
+        </is>
+      </c>
       <c r="K41" s="7" t="n">
-        <v>7432.03</v>
+        <v>6645.86</v>
       </c>
       <c r="L41" s="7" t="n">
-        <v>3716</v>
+        <v>6645</v>
       </c>
     </row>
     <row r="42">
@@ -2158,7 +2174,7 @@
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>71-9629</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
@@ -2182,17 +2198,17 @@
       <c r="G42" s="9" t="n"/>
       <c r="H42" s="9" t="inlineStr">
         <is>
-          <t>รอปลายทางข้ามคืน Dest_In→Dest_Out (20.96h); เต็ม 1 เที่ยว (เรทวัน Dest_In)</t>
+          <t>รอปลายทางข้ามคืน Dest_In→Dest_Out (18.79h); เต็ม 1 เที่ยว (เรทวัน Dest_In)</t>
         </is>
       </c>
       <c r="I42" s="9" t="inlineStr">
         <is>
-          <t>2026-04-21 16:38:59</t>
+          <t>2026-04-21 09:15:51</t>
         </is>
       </c>
       <c r="J42" s="9" t="inlineStr">
         <is>
-          <t>2026-04-22 13:36:47</t>
+          <t>2026-04-22 04:03:28</t>
         </is>
       </c>
       <c r="K42" s="10" t="n">
@@ -2202,108 +2218,8 @@
         <v>6645</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="5" t="n">
-        <v>46133</v>
-      </c>
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>71-8681</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>LCB</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>midnight_full</t>
-        </is>
-      </c>
-      <c r="E43" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" s="6" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G43" s="6" t="n"/>
-      <c r="H43" s="6" t="inlineStr">
-        <is>
-          <t>รอปลายทางข้ามคืน Dest_In→Dest_Out (21.30h); เต็ม 1 เที่ยว (เรทวัน Dest_In)</t>
-        </is>
-      </c>
-      <c r="I43" s="6" t="inlineStr">
-        <is>
-          <t>2026-04-21 13:37:02</t>
-        </is>
-      </c>
-      <c r="J43" s="6" t="inlineStr">
-        <is>
-          <t>2026-04-22 10:55:11</t>
-        </is>
-      </c>
-      <c r="K43" s="7" t="n">
-        <v>6645.86</v>
-      </c>
-      <c r="L43" s="7" t="n">
-        <v>6645</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="8" t="n">
-        <v>46133</v>
-      </c>
-      <c r="B44" s="9" t="inlineStr">
-        <is>
-          <t>71-9629</t>
-        </is>
-      </c>
-      <c r="C44" s="9" t="inlineStr">
-        <is>
-          <t>LCB</t>
-        </is>
-      </c>
-      <c r="D44" s="9" t="inlineStr">
-        <is>
-          <t>midnight_full</t>
-        </is>
-      </c>
-      <c r="E44" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F44" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G44" s="9" t="n"/>
-      <c r="H44" s="9" t="inlineStr">
-        <is>
-          <t>รอปลายทางข้ามคืน Dest_In→Dest_Out (18.79h); เต็ม 1 เที่ยว (เรทวัน Dest_In)</t>
-        </is>
-      </c>
-      <c r="I44" s="9" t="inlineStr">
-        <is>
-          <t>2026-04-21 09:15:51</t>
-        </is>
-      </c>
-      <c r="J44" s="9" t="inlineStr">
-        <is>
-          <t>2026-04-22 04:03:28</t>
-        </is>
-      </c>
-      <c r="K44" s="10" t="n">
-        <v>6645.86</v>
-      </c>
-      <c r="L44" s="10" t="n">
-        <v>6645</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:L44"/>
+  <autoFilter ref="A4:L42"/>
   <mergeCells count="1">
     <mergeCell ref="A1:L1"/>
   </mergeCells>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/09_Surcharge_50pct_1Trip.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/09_Surcharge_50pct_1Trip.xlsx
@@ -518,7 +518,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-08 18:39</t>
+          <t>2026-05-09 00:22</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/09_Surcharge_50pct_1Trip.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/09_Surcharge_50pct_1Trip.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Surcharge_50pct_1Trip" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Surcharge_50pct_1Trip" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Surcharge_50pct_1Trip'!$A$4:$L$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Surcharge_50pct_1Trip'!$A$4:$L$78</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L42"/>
+  <dimension ref="A1:L78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -496,9 +496,9 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
     <col width="17" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
-    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="22" customWidth="1" min="12" max="12"/>
   </cols>
@@ -518,7 +518,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-09 00:22</t>
+          <t>2026-06-04 19:42</t>
         </is>
       </c>
     </row>
@@ -600,11 +600,11 @@
     </row>
     <row r="5">
       <c r="A5" s="5" t="n">
-        <v>46123</v>
+        <v>46143</v>
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C5" s="6" t="inlineStr">
@@ -629,24 +629,24 @@
       <c r="H5" s="6" t="n"/>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="J5" s="6" t="n"/>
       <c r="K5" s="7" t="n">
-        <v>6849.81</v>
+        <v>7432.03</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>3425</v>
+        <v>3716</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="n">
-        <v>46123</v>
+        <v>46143</v>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>71-8683</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
@@ -671,29 +671,29 @@
       <c r="H6" s="9" t="n"/>
       <c r="I6" s="9" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="J6" s="9" t="n"/>
       <c r="K6" s="10" t="n">
-        <v>6849.81</v>
+        <v>7432.03</v>
       </c>
       <c r="L6" s="10" t="n">
-        <v>3425</v>
+        <v>3716</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>46122</v>
+        <v>46145</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>71-8684</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
@@ -713,29 +713,29 @@
       <c r="H7" s="6" t="n"/>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="J7" s="6" t="n"/>
       <c r="K7" s="7" t="n">
-        <v>7276.69</v>
+        <v>7432.03</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>3638</v>
+        <v>3716</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="n">
-        <v>46124</v>
+        <v>46144</v>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>71-6802</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
@@ -755,29 +755,29 @@
       <c r="H8" s="9" t="n"/>
       <c r="I8" s="9" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="J8" s="9" t="n"/>
       <c r="K8" s="10" t="n">
-        <v>7306.47</v>
+        <v>7432.03</v>
       </c>
       <c r="L8" s="10" t="n">
-        <v>3653</v>
+        <v>3716</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
-        <v>46124</v>
+        <v>46146</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -797,29 +797,29 @@
       <c r="H9" s="6" t="n"/>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="J9" s="6" t="n"/>
       <c r="K9" s="7" t="n">
-        <v>7306.47</v>
+        <v>7432.03</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>3653</v>
+        <v>3716</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="n">
-        <v>46124</v>
+        <v>46145</v>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
@@ -839,24 +839,24 @@
       <c r="H10" s="9" t="n"/>
       <c r="I10" s="9" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="J10" s="9" t="n"/>
       <c r="K10" s="10" t="n">
-        <v>7306.47</v>
+        <v>7432.03</v>
       </c>
       <c r="L10" s="10" t="n">
-        <v>3653</v>
+        <v>3716</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>46125</v>
+        <v>46146</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>71-8681</t>
+          <t>71-6802</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -881,24 +881,24 @@
       <c r="H11" s="6" t="n"/>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="J11" s="6" t="n"/>
       <c r="K11" s="7" t="n">
-        <v>7306.47</v>
+        <v>7432.03</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>3653</v>
+        <v>3716</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="n">
-        <v>46124</v>
+        <v>46146</v>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>71-8684</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
@@ -923,29 +923,29 @@
       <c r="H12" s="9" t="n"/>
       <c r="I12" s="9" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="J12" s="9" t="n"/>
       <c r="K12" s="10" t="n">
-        <v>7306.47</v>
+        <v>7432.03</v>
       </c>
       <c r="L12" s="10" t="n">
-        <v>3653</v>
+        <v>3716</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
-        <v>46125</v>
+        <v>46146</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>71-9629</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
@@ -965,24 +965,24 @@
       <c r="H13" s="6" t="n"/>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="J13" s="6" t="n"/>
       <c r="K13" s="7" t="n">
-        <v>7306.47</v>
+        <v>7432.03</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>3653</v>
+        <v>3716</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="n">
-        <v>46125</v>
+        <v>46146</v>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-6802</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
@@ -1007,29 +1007,29 @@
       <c r="H14" s="9" t="n"/>
       <c r="I14" s="9" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="J14" s="9" t="n"/>
       <c r="K14" s="10" t="n">
-        <v>7306.47</v>
+        <v>7432.03</v>
       </c>
       <c r="L14" s="10" t="n">
-        <v>3653</v>
+        <v>3716</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
-        <v>46125</v>
+        <v>46147</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
@@ -1049,24 +1049,24 @@
       <c r="H15" s="6" t="n"/>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="J15" s="6" t="n"/>
       <c r="K15" s="7" t="n">
-        <v>7306.47</v>
+        <v>7432.03</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>3653</v>
+        <v>3716</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="n">
-        <v>46126</v>
+        <v>46147</v>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>71-8681</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
@@ -1091,24 +1091,24 @@
       <c r="H16" s="9" t="n"/>
       <c r="I16" s="9" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="J16" s="9" t="n"/>
       <c r="K16" s="10" t="n">
-        <v>7306.47</v>
+        <v>7432.03</v>
       </c>
       <c r="L16" s="10" t="n">
-        <v>3653</v>
+        <v>3716</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
-        <v>46127</v>
+        <v>46148</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -1133,24 +1133,24 @@
       <c r="H17" s="6" t="n"/>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="J17" s="6" t="n"/>
       <c r="K17" s="7" t="n">
-        <v>7306.47</v>
+        <v>7432.03</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>3653</v>
+        <v>3716</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="n">
-        <v>46127</v>
+        <v>46148</v>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>71-8681</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
@@ -1175,29 +1175,29 @@
       <c r="H18" s="9" t="n"/>
       <c r="I18" s="9" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="J18" s="9" t="n"/>
       <c r="K18" s="10" t="n">
-        <v>7306.47</v>
+        <v>7432.03</v>
       </c>
       <c r="L18" s="10" t="n">
-        <v>3653</v>
+        <v>3716</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="n">
-        <v>46126</v>
+        <v>46149</v>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>72-1220</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -1217,29 +1217,29 @@
       <c r="H19" s="6" t="n"/>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="J19" s="6" t="n"/>
       <c r="K19" s="7" t="n">
-        <v>7306.47</v>
+        <v>7432.03</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>3653</v>
+        <v>3716</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="n">
-        <v>46128</v>
+        <v>46149</v>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>71-8681</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
@@ -1259,24 +1259,24 @@
       <c r="H20" s="9" t="n"/>
       <c r="I20" s="9" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="J20" s="9" t="n"/>
       <c r="K20" s="10" t="n">
-        <v>6849.81</v>
+        <v>7432.03</v>
       </c>
       <c r="L20" s="10" t="n">
-        <v>3425</v>
+        <v>3716</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="n">
-        <v>46128</v>
+        <v>46149</v>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>71-9629</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1301,29 +1301,29 @@
       <c r="H21" s="6" t="n"/>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="J21" s="6" t="n"/>
       <c r="K21" s="7" t="n">
-        <v>6849.81</v>
+        <v>7432.03</v>
       </c>
       <c r="L21" s="7" t="n">
-        <v>3425</v>
+        <v>3716</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="n">
-        <v>46127</v>
+        <v>46151</v>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>72-1220</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
@@ -1343,29 +1343,29 @@
       <c r="H22" s="9" t="n"/>
       <c r="I22" s="9" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="J22" s="9" t="n"/>
       <c r="K22" s="10" t="n">
-        <v>7306.47</v>
+        <v>7322.2</v>
       </c>
       <c r="L22" s="10" t="n">
-        <v>3653</v>
+        <v>3661</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="n">
-        <v>46129</v>
+        <v>46150</v>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>71-8681</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -1385,29 +1385,29 @@
       <c r="H23" s="6" t="n"/>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="J23" s="6" t="n"/>
       <c r="K23" s="7" t="n">
-        <v>6645.86</v>
+        <v>7322.2</v>
       </c>
       <c r="L23" s="7" t="n">
-        <v>3323</v>
+        <v>3661</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="n">
-        <v>46131</v>
+        <v>46152</v>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>71-8681</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
@@ -1427,29 +1427,29 @@
       <c r="H24" s="9" t="n"/>
       <c r="I24" s="9" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="J24" s="9" t="n"/>
       <c r="K24" s="10" t="n">
-        <v>6645.86</v>
+        <v>7322.2</v>
       </c>
       <c r="L24" s="10" t="n">
-        <v>3323</v>
+        <v>3661</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
-        <v>46133</v>
+        <v>46151</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -1469,29 +1469,29 @@
       <c r="H25" s="6" t="n"/>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="J25" s="6" t="n"/>
       <c r="K25" s="7" t="n">
-        <v>6546.17</v>
+        <v>7322.2</v>
       </c>
       <c r="L25" s="7" t="n">
-        <v>3273</v>
+        <v>3661</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="n">
-        <v>46134</v>
+        <v>46152</v>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
@@ -1511,29 +1511,29 @@
       <c r="H26" s="9" t="n"/>
       <c r="I26" s="9" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="J26" s="9" t="n"/>
       <c r="K26" s="10" t="n">
-        <v>6546.17</v>
+        <v>7322.2</v>
       </c>
       <c r="L26" s="10" t="n">
-        <v>3273</v>
+        <v>3661</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
-        <v>46134</v>
+        <v>46151</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
@@ -1553,29 +1553,29 @@
       <c r="H27" s="6" t="n"/>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="J27" s="6" t="n"/>
       <c r="K27" s="7" t="n">
-        <v>6546.17</v>
+        <v>7322.2</v>
       </c>
       <c r="L27" s="7" t="n">
-        <v>3273</v>
+        <v>3661</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="n">
-        <v>46134</v>
+        <v>46152</v>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
@@ -1595,24 +1595,24 @@
       <c r="H28" s="9" t="n"/>
       <c r="I28" s="9" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="J28" s="9" t="n"/>
       <c r="K28" s="10" t="n">
-        <v>6546.17</v>
+        <v>7322.2</v>
       </c>
       <c r="L28" s="10" t="n">
-        <v>3273</v>
+        <v>3661</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="n">
-        <v>46135</v>
+        <v>46152</v>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>71-8681</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
@@ -1637,29 +1637,29 @@
       <c r="H29" s="6" t="n"/>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="J29" s="6" t="n"/>
       <c r="K29" s="7" t="n">
-        <v>6546.17</v>
+        <v>7322.2</v>
       </c>
       <c r="L29" s="7" t="n">
-        <v>3273</v>
+        <v>3661</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="n">
-        <v>46134</v>
+        <v>46154</v>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>71-9629</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C30" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
@@ -1679,29 +1679,29 @@
       <c r="H30" s="9" t="n"/>
       <c r="I30" s="9" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="J30" s="9" t="n"/>
       <c r="K30" s="10" t="n">
-        <v>6546.17</v>
+        <v>7322.2</v>
       </c>
       <c r="L30" s="10" t="n">
-        <v>3273</v>
+        <v>3661</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
-        <v>46134</v>
+        <v>46155</v>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
@@ -1721,29 +1721,29 @@
       <c r="H31" s="6" t="n"/>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="J31" s="6" t="n"/>
       <c r="K31" s="7" t="n">
-        <v>6546.17</v>
+        <v>7432.03</v>
       </c>
       <c r="L31" s="7" t="n">
-        <v>3273</v>
+        <v>3716</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="n">
-        <v>46137</v>
+        <v>46157</v>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C32" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
@@ -1763,29 +1763,29 @@
       <c r="H32" s="9" t="n"/>
       <c r="I32" s="9" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="J32" s="9" t="n"/>
       <c r="K32" s="10" t="n">
-        <v>6500</v>
+        <v>7543.52</v>
       </c>
       <c r="L32" s="10" t="n">
-        <v>3250</v>
+        <v>3772</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
-        <v>46138</v>
+        <v>46156</v>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>71-8681</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
@@ -1805,24 +1805,24 @@
       <c r="H33" s="6" t="n"/>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="J33" s="6" t="n"/>
       <c r="K33" s="7" t="n">
-        <v>6500</v>
+        <v>7543.52</v>
       </c>
       <c r="L33" s="7" t="n">
-        <v>3250</v>
+        <v>3772</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="n">
-        <v>46137</v>
+        <v>46156</v>
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>71-9629</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
@@ -1847,24 +1847,24 @@
       <c r="H34" s="9" t="n"/>
       <c r="I34" s="9" t="inlineStr">
         <is>
-          <t>2026-04-25</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="J34" s="9" t="n"/>
       <c r="K34" s="10" t="n">
-        <v>6500</v>
+        <v>7543.52</v>
       </c>
       <c r="L34" s="10" t="n">
-        <v>3250</v>
+        <v>3772</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
-        <v>46138</v>
+        <v>46158</v>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>71-9629</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
@@ -1889,24 +1889,24 @@
       <c r="H35" s="6" t="n"/>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="J35" s="6" t="n"/>
       <c r="K35" s="7" t="n">
-        <v>6500</v>
+        <v>7543.52</v>
       </c>
       <c r="L35" s="7" t="n">
-        <v>3250</v>
+        <v>3772</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="n">
-        <v>46141</v>
+        <v>46160</v>
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
@@ -1931,29 +1931,29 @@
       <c r="H36" s="9" t="n"/>
       <c r="I36" s="9" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="J36" s="9" t="n"/>
       <c r="K36" s="10" t="n">
-        <v>6500</v>
+        <v>7543.52</v>
       </c>
       <c r="L36" s="10" t="n">
-        <v>3250</v>
+        <v>3772</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="n">
-        <v>46142</v>
+        <v>46161</v>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
@@ -1973,29 +1973,29 @@
       <c r="H37" s="6" t="n"/>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="J37" s="6" t="n"/>
       <c r="K37" s="7" t="n">
-        <v>6500</v>
+        <v>7656.67</v>
       </c>
       <c r="L37" s="7" t="n">
-        <v>3250</v>
+        <v>3828</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="n">
-        <v>46141</v>
+        <v>46161</v>
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>71-8681</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
@@ -2015,24 +2015,24 @@
       <c r="H38" s="9" t="n"/>
       <c r="I38" s="9" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="J38" s="9" t="n"/>
       <c r="K38" s="10" t="n">
-        <v>6500</v>
+        <v>7656.67</v>
       </c>
       <c r="L38" s="10" t="n">
-        <v>3250</v>
+        <v>3828</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n">
-        <v>46141</v>
+        <v>46161</v>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>71-9629</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
@@ -2057,34 +2057,34 @@
       <c r="H39" s="6" t="n"/>
       <c r="I39" s="6" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="J39" s="6" t="n"/>
       <c r="K39" s="7" t="n">
-        <v>6500</v>
+        <v>7656.67</v>
       </c>
       <c r="L39" s="7" t="n">
-        <v>3250</v>
+        <v>3828</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="n">
-        <v>46133</v>
+        <v>46161</v>
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>midnight_full</t>
+          <t>downtime_origin_day</t>
         </is>
       </c>
       <c r="E40" s="9" t="n">
@@ -2092,49 +2092,41 @@
       </c>
       <c r="F40" s="9" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G40" s="9" t="n"/>
-      <c r="H40" s="9" t="inlineStr">
-        <is>
-          <t>รอปลายทางข้ามคืน Dest_In→Dest_Out (20.96h); เต็ม 1 เที่ยว (เรทวัน Dest_In)</t>
-        </is>
-      </c>
+      <c r="H40" s="9" t="n"/>
       <c r="I40" s="9" t="inlineStr">
         <is>
-          <t>2026-04-21 16:38:59</t>
-        </is>
-      </c>
-      <c r="J40" s="9" t="inlineStr">
-        <is>
-          <t>2026-04-22 13:36:47</t>
-        </is>
-      </c>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="J40" s="9" t="n"/>
       <c r="K40" s="10" t="n">
-        <v>6645.86</v>
+        <v>7656.67</v>
       </c>
       <c r="L40" s="10" t="n">
-        <v>6645</v>
+        <v>3828</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="n">
-        <v>46133</v>
+        <v>46161</v>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>71-8681</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>midnight_full</t>
+          <t>downtime_origin_day</t>
         </is>
       </c>
       <c r="E41" s="6" t="n">
@@ -2142,84 +2134,1580 @@
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G41" s="6" t="n"/>
-      <c r="H41" s="6" t="inlineStr">
-        <is>
-          <t>รอปลายทางข้ามคืน Dest_In→Dest_Out (21.30h); เต็ม 1 เที่ยว (เรทวัน Dest_In)</t>
-        </is>
-      </c>
+      <c r="H41" s="6" t="n"/>
       <c r="I41" s="6" t="inlineStr">
         <is>
-          <t>2026-04-21 13:37:02</t>
-        </is>
-      </c>
-      <c r="J41" s="6" t="inlineStr">
-        <is>
-          <t>2026-04-22 10:55:11</t>
-        </is>
-      </c>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="n"/>
       <c r="K41" s="7" t="n">
-        <v>6645.86</v>
+        <v>7656.67</v>
       </c>
       <c r="L41" s="7" t="n">
-        <v>6645</v>
+        <v>3828</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="n">
-        <v>46133</v>
+        <v>46162</v>
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>71-9629</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
         <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>downtime_origin_day</t>
+        </is>
+      </c>
+      <c r="E42" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G42" s="9" t="n"/>
+      <c r="H42" s="9" t="n"/>
+      <c r="I42" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="J42" s="9" t="n"/>
+      <c r="K42" s="10" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="L42" s="10" t="n">
+        <v>3828</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>71-8001</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>downtime_origin_day</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="n"/>
+      <c r="H43" s="6" t="n"/>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="J43" s="6" t="n"/>
+      <c r="K43" s="7" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="L43" s="7" t="n">
+        <v>3828</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>71-8005</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="inlineStr">
+        <is>
+          <t>downtime_origin_day</t>
+        </is>
+      </c>
+      <c r="E44" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G44" s="9" t="n"/>
+      <c r="H44" s="9" t="n"/>
+      <c r="I44" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="J44" s="9" t="n"/>
+      <c r="K44" s="10" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="L44" s="10" t="n">
+        <v>3828</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>downtime_origin_day</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="n"/>
+      <c r="H45" s="6" t="n"/>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="n"/>
+      <c r="K45" s="7" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="L45" s="7" t="n">
+        <v>3828</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="8" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>72-1217</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
           <t>LCB</t>
         </is>
       </c>
-      <c r="D42" s="9" t="inlineStr">
-        <is>
-          <t>midnight_full</t>
-        </is>
-      </c>
-      <c r="E42" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F42" s="9" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="G42" s="9" t="n"/>
-      <c r="H42" s="9" t="inlineStr">
-        <is>
-          <t>รอปลายทางข้ามคืน Dest_In→Dest_Out (18.79h); เต็ม 1 เที่ยว (เรทวัน Dest_In)</t>
-        </is>
-      </c>
-      <c r="I42" s="9" t="inlineStr">
-        <is>
-          <t>2026-04-21 09:15:51</t>
-        </is>
-      </c>
-      <c r="J42" s="9" t="inlineStr">
-        <is>
-          <t>2026-04-22 04:03:28</t>
-        </is>
-      </c>
-      <c r="K42" s="10" t="n">
-        <v>6645.86</v>
-      </c>
-      <c r="L42" s="10" t="n">
-        <v>6645</v>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>downtime_origin_day</t>
+        </is>
+      </c>
+      <c r="E46" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G46" s="9" t="n"/>
+      <c r="H46" s="9" t="n"/>
+      <c r="I46" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="J46" s="9" t="n"/>
+      <c r="K46" s="10" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="L46" s="10" t="n">
+        <v>3828</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>71-8005</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>downtime_origin_day</t>
+        </is>
+      </c>
+      <c r="E47" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="n"/>
+      <c r="H47" s="6" t="n"/>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="J47" s="6" t="n"/>
+      <c r="K47" s="7" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="L47" s="7" t="n">
+        <v>3828</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="8" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>downtime_origin_day</t>
+        </is>
+      </c>
+      <c r="E48" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G48" s="9" t="n"/>
+      <c r="H48" s="9" t="n"/>
+      <c r="I48" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="J48" s="9" t="n"/>
+      <c r="K48" s="10" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="L48" s="10" t="n">
+        <v>3828</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>71-8002</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>downtime_origin_day</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="n"/>
+      <c r="H49" s="6" t="n"/>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="n"/>
+      <c r="K49" s="7" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="L49" s="7" t="n">
+        <v>3828</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>71-8005</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>downtime_origin_day</t>
+        </is>
+      </c>
+      <c r="E50" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G50" s="9" t="n"/>
+      <c r="H50" s="9" t="n"/>
+      <c r="I50" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="J50" s="9" t="n"/>
+      <c r="K50" s="10" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="L50" s="10" t="n">
+        <v>3828</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>downtime_origin_day</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="n"/>
+      <c r="H51" s="6" t="n"/>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="J51" s="6" t="n"/>
+      <c r="K51" s="7" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="L51" s="7" t="n">
+        <v>3828</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B52" s="9" t="inlineStr">
+        <is>
+          <t>71-8001</t>
+        </is>
+      </c>
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="inlineStr">
+        <is>
+          <t>downtime_origin_day</t>
+        </is>
+      </c>
+      <c r="E52" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G52" s="9" t="n"/>
+      <c r="H52" s="9" t="n"/>
+      <c r="I52" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="J52" s="9" t="n"/>
+      <c r="K52" s="10" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="L52" s="10" t="n">
+        <v>3828</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>71-8002</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>downtime_origin_day</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="n"/>
+      <c r="H53" s="6" t="n"/>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="J53" s="6" t="n"/>
+      <c r="K53" s="7" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="L53" s="7" t="n">
+        <v>3828</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="8" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>71-8005</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="inlineStr">
+        <is>
+          <t>downtime_origin_day</t>
+        </is>
+      </c>
+      <c r="E54" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G54" s="9" t="n"/>
+      <c r="H54" s="9" t="n"/>
+      <c r="I54" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="J54" s="9" t="n"/>
+      <c r="K54" s="10" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="L54" s="10" t="n">
+        <v>3828</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>72-1217</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>LCB</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>downtime_origin_day</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="n"/>
+      <c r="H55" s="6" t="n"/>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-23</t>
+        </is>
+      </c>
+      <c r="J55" s="6" t="n"/>
+      <c r="K55" s="7" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="L55" s="7" t="n">
+        <v>3828</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B56" s="9" t="inlineStr">
+        <is>
+          <t>71-8001</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="inlineStr">
+        <is>
+          <t>downtime_origin_day</t>
+        </is>
+      </c>
+      <c r="E56" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G56" s="9" t="n"/>
+      <c r="H56" s="9" t="n"/>
+      <c r="I56" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="J56" s="9" t="n"/>
+      <c r="K56" s="10" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="L56" s="10" t="n">
+        <v>3828</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>71-8005</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>downtime_origin_day</t>
+        </is>
+      </c>
+      <c r="E57" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G57" s="6" t="n"/>
+      <c r="H57" s="6" t="n"/>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="J57" s="6" t="n"/>
+      <c r="K57" s="7" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="L57" s="7" t="n">
+        <v>3828</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="8" t="n">
+        <v>46167</v>
+      </c>
+      <c r="B58" s="9" t="inlineStr">
+        <is>
+          <t>71-8005</t>
+        </is>
+      </c>
+      <c r="C58" s="9" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="inlineStr">
+        <is>
+          <t>downtime_origin_day</t>
+        </is>
+      </c>
+      <c r="E58" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G58" s="9" t="n"/>
+      <c r="H58" s="9" t="n"/>
+      <c r="I58" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="J58" s="9" t="n"/>
+      <c r="K58" s="10" t="n">
+        <v>7656.67</v>
+      </c>
+      <c r="L58" s="10" t="n">
+        <v>3828</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B59" s="6" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>downtime_origin_day</t>
+        </is>
+      </c>
+      <c r="E59" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="n"/>
+      <c r="H59" s="6" t="n"/>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="J59" s="6" t="n"/>
+      <c r="K59" s="7" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="L59" s="7" t="n">
+        <v>3772</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="8" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B60" s="9" t="inlineStr">
+        <is>
+          <t>72-1217</t>
+        </is>
+      </c>
+      <c r="C60" s="9" t="inlineStr">
+        <is>
+          <t>LCB</t>
+        </is>
+      </c>
+      <c r="D60" s="9" t="inlineStr">
+        <is>
+          <t>downtime_origin_day</t>
+        </is>
+      </c>
+      <c r="E60" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G60" s="9" t="n"/>
+      <c r="H60" s="9" t="n"/>
+      <c r="I60" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="J60" s="9" t="n"/>
+      <c r="K60" s="10" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="L60" s="10" t="n">
+        <v>3772</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="n">
+        <v>46169</v>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>71-8002</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>downtime_origin_day</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="n"/>
+      <c r="H61" s="6" t="n"/>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="J61" s="6" t="n"/>
+      <c r="K61" s="7" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="L61" s="7" t="n">
+        <v>3772</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="8" t="n">
+        <v>46169</v>
+      </c>
+      <c r="B62" s="9" t="inlineStr">
+        <is>
+          <t>71-8003</t>
+        </is>
+      </c>
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D62" s="9" t="inlineStr">
+        <is>
+          <t>downtime_origin_day</t>
+        </is>
+      </c>
+      <c r="E62" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G62" s="9" t="n"/>
+      <c r="H62" s="9" t="n"/>
+      <c r="I62" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="J62" s="9" t="n"/>
+      <c r="K62" s="10" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="L62" s="10" t="n">
+        <v>3772</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>71-8005</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>downtime_origin_day</t>
+        </is>
+      </c>
+      <c r="E63" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="n"/>
+      <c r="H63" s="6" t="n"/>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="J63" s="6" t="n"/>
+      <c r="K63" s="7" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="L63" s="7" t="n">
+        <v>3772</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="8" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B64" s="9" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C64" s="9" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D64" s="9" t="inlineStr">
+        <is>
+          <t>downtime_origin_day</t>
+        </is>
+      </c>
+      <c r="E64" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F64" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G64" s="9" t="n"/>
+      <c r="H64" s="9" t="n"/>
+      <c r="I64" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="J64" s="9" t="n"/>
+      <c r="K64" s="10" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="L64" s="10" t="n">
+        <v>3772</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B65" s="6" t="inlineStr">
+        <is>
+          <t>72-1217</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>LCB</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>downtime_origin_day</t>
+        </is>
+      </c>
+      <c r="E65" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="n"/>
+      <c r="H65" s="6" t="n"/>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="J65" s="6" t="n"/>
+      <c r="K65" s="7" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="L65" s="7" t="n">
+        <v>3772</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="8" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B66" s="9" t="inlineStr">
+        <is>
+          <t>71-8001</t>
+        </is>
+      </c>
+      <c r="C66" s="9" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D66" s="9" t="inlineStr">
+        <is>
+          <t>downtime_origin_day</t>
+        </is>
+      </c>
+      <c r="E66" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F66" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G66" s="9" t="n"/>
+      <c r="H66" s="9" t="n"/>
+      <c r="I66" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="J66" s="9" t="n"/>
+      <c r="K66" s="10" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="L66" s="10" t="n">
+        <v>3772</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>71-8002</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="inlineStr">
+        <is>
+          <t>downtime_origin_day</t>
+        </is>
+      </c>
+      <c r="E67" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="n"/>
+      <c r="H67" s="6" t="n"/>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="J67" s="6" t="n"/>
+      <c r="K67" s="7" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="L67" s="7" t="n">
+        <v>3772</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="8" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B68" s="9" t="inlineStr">
+        <is>
+          <t>71-8003</t>
+        </is>
+      </c>
+      <c r="C68" s="9" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="inlineStr">
+        <is>
+          <t>downtime_origin_day</t>
+        </is>
+      </c>
+      <c r="E68" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G68" s="9" t="n"/>
+      <c r="H68" s="9" t="n"/>
+      <c r="I68" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="J68" s="9" t="n"/>
+      <c r="K68" s="10" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="L68" s="10" t="n">
+        <v>3772</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="n">
+        <v>46169</v>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>72-1217</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>LCB</t>
+        </is>
+      </c>
+      <c r="D69" s="6" t="inlineStr">
+        <is>
+          <t>downtime_origin_day</t>
+        </is>
+      </c>
+      <c r="E69" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="n"/>
+      <c r="H69" s="6" t="n"/>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="J69" s="6" t="n"/>
+      <c r="K69" s="7" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="L69" s="7" t="n">
+        <v>3772</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="8" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B70" s="9" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="inlineStr">
+        <is>
+          <t>downtime_origin_day</t>
+        </is>
+      </c>
+      <c r="E70" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G70" s="9" t="n"/>
+      <c r="H70" s="9" t="n"/>
+      <c r="I70" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="J70" s="9" t="n"/>
+      <c r="K70" s="10" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="L70" s="10" t="n">
+        <v>3772</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>72-1217</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>LCB</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>downtime_origin_day</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G71" s="6" t="n"/>
+      <c r="H71" s="6" t="n"/>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="J71" s="6" t="n"/>
+      <c r="K71" s="7" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="L71" s="7" t="n">
+        <v>3772</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="8" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B72" s="9" t="inlineStr">
+        <is>
+          <t>71-8003</t>
+        </is>
+      </c>
+      <c r="C72" s="9" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="inlineStr">
+        <is>
+          <t>downtime_origin_day</t>
+        </is>
+      </c>
+      <c r="E72" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F72" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G72" s="9" t="n"/>
+      <c r="H72" s="9" t="n"/>
+      <c r="I72" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="J72" s="9" t="n"/>
+      <c r="K72" s="10" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="L72" s="10" t="n">
+        <v>3772</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>72-1217</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>LCB</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>downtime_origin_day</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="n"/>
+      <c r="H73" s="6" t="n"/>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="J73" s="6" t="n"/>
+      <c r="K73" s="7" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="L73" s="7" t="n">
+        <v>3772</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="8" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B74" s="9" t="inlineStr">
+        <is>
+          <t>71-8003</t>
+        </is>
+      </c>
+      <c r="C74" s="9" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D74" s="9" t="inlineStr">
+        <is>
+          <t>downtime_origin_day</t>
+        </is>
+      </c>
+      <c r="E74" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G74" s="9" t="n"/>
+      <c r="H74" s="9" t="n"/>
+      <c r="I74" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="J74" s="9" t="n"/>
+      <c r="K74" s="10" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="L74" s="10" t="n">
+        <v>3772</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>downtime_origin_day</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G75" s="6" t="n"/>
+      <c r="H75" s="6" t="n"/>
+      <c r="I75" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="J75" s="6" t="n"/>
+      <c r="K75" s="7" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="L75" s="7" t="n">
+        <v>3772</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="8" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B76" s="9" t="inlineStr">
+        <is>
+          <t>72-1217</t>
+        </is>
+      </c>
+      <c r="C76" s="9" t="inlineStr">
+        <is>
+          <t>LCB</t>
+        </is>
+      </c>
+      <c r="D76" s="9" t="inlineStr">
+        <is>
+          <t>downtime_origin_day</t>
+        </is>
+      </c>
+      <c r="E76" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F76" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G76" s="9" t="n"/>
+      <c r="H76" s="9" t="n"/>
+      <c r="I76" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="J76" s="9" t="n"/>
+      <c r="K76" s="10" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="L76" s="10" t="n">
+        <v>3772</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="5" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>71-5042</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>downtime_origin_day</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="n"/>
+      <c r="H77" s="6" t="n"/>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="J77" s="6" t="n"/>
+      <c r="K77" s="7" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="L77" s="7" t="n">
+        <v>3772</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="8" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B78" s="9" t="inlineStr">
+        <is>
+          <t>72-1217</t>
+        </is>
+      </c>
+      <c r="C78" s="9" t="inlineStr">
+        <is>
+          <t>LCB</t>
+        </is>
+      </c>
+      <c r="D78" s="9" t="inlineStr">
+        <is>
+          <t>downtime_origin_day</t>
+        </is>
+      </c>
+      <c r="E78" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F78" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G78" s="9" t="n"/>
+      <c r="H78" s="9" t="n"/>
+      <c r="I78" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="J78" s="9" t="n"/>
+      <c r="K78" s="10" t="n">
+        <v>7543.52</v>
+      </c>
+      <c r="L78" s="10" t="n">
+        <v>3772</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:L42"/>
+  <autoFilter ref="A4:L78"/>
   <mergeCells count="1">
     <mergeCell ref="A1:L1"/>
   </mergeCells>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/09_Surcharge_50pct_1Trip.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/09_Surcharge_50pct_1Trip.xlsx
@@ -518,7 +518,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04 19:42</t>
+          <t>2026-06-05 14:46</t>
         </is>
       </c>
     </row>
@@ -634,10 +634,10 @@
       </c>
       <c r="J5" s="6" t="n"/>
       <c r="K5" s="7" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>3716</v>
+        <v>3689</v>
       </c>
     </row>
     <row r="6">
@@ -676,10 +676,10 @@
       </c>
       <c r="J6" s="9" t="n"/>
       <c r="K6" s="10" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="L6" s="10" t="n">
-        <v>3716</v>
+        <v>3689</v>
       </c>
     </row>
     <row r="7">
@@ -718,10 +718,10 @@
       </c>
       <c r="J7" s="6" t="n"/>
       <c r="K7" s="7" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>3716</v>
+        <v>3689</v>
       </c>
     </row>
     <row r="8">
@@ -760,10 +760,10 @@
       </c>
       <c r="J8" s="9" t="n"/>
       <c r="K8" s="10" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="L8" s="10" t="n">
-        <v>3716</v>
+        <v>3689</v>
       </c>
     </row>
     <row r="9">
@@ -802,10 +802,10 @@
       </c>
       <c r="J9" s="6" t="n"/>
       <c r="K9" s="7" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>3716</v>
+        <v>3689</v>
       </c>
     </row>
     <row r="10">
@@ -844,10 +844,10 @@
       </c>
       <c r="J10" s="9" t="n"/>
       <c r="K10" s="10" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="L10" s="10" t="n">
-        <v>3716</v>
+        <v>3689</v>
       </c>
     </row>
     <row r="11">
@@ -886,10 +886,10 @@
       </c>
       <c r="J11" s="6" t="n"/>
       <c r="K11" s="7" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>3716</v>
+        <v>3689</v>
       </c>
     </row>
     <row r="12">
@@ -928,10 +928,10 @@
       </c>
       <c r="J12" s="9" t="n"/>
       <c r="K12" s="10" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="L12" s="10" t="n">
-        <v>3716</v>
+        <v>3689</v>
       </c>
     </row>
     <row r="13">
@@ -970,10 +970,10 @@
       </c>
       <c r="J13" s="6" t="n"/>
       <c r="K13" s="7" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>3716</v>
+        <v>3689</v>
       </c>
     </row>
     <row r="14">
@@ -1012,10 +1012,10 @@
       </c>
       <c r="J14" s="9" t="n"/>
       <c r="K14" s="10" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="L14" s="10" t="n">
-        <v>3716</v>
+        <v>3689</v>
       </c>
     </row>
     <row r="15">
@@ -1054,10 +1054,10 @@
       </c>
       <c r="J15" s="6" t="n"/>
       <c r="K15" s="7" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>3716</v>
+        <v>3689</v>
       </c>
     </row>
     <row r="16">
@@ -1096,10 +1096,10 @@
       </c>
       <c r="J16" s="9" t="n"/>
       <c r="K16" s="10" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="L16" s="10" t="n">
-        <v>3716</v>
+        <v>3689</v>
       </c>
     </row>
     <row r="17">
@@ -1138,10 +1138,10 @@
       </c>
       <c r="J17" s="6" t="n"/>
       <c r="K17" s="7" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>3716</v>
+        <v>3689</v>
       </c>
     </row>
     <row r="18">
@@ -1180,10 +1180,10 @@
       </c>
       <c r="J18" s="9" t="n"/>
       <c r="K18" s="10" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="L18" s="10" t="n">
-        <v>3716</v>
+        <v>3689</v>
       </c>
     </row>
     <row r="19">
@@ -1222,10 +1222,10 @@
       </c>
       <c r="J19" s="6" t="n"/>
       <c r="K19" s="7" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>3716</v>
+        <v>3689</v>
       </c>
     </row>
     <row r="20">
@@ -1264,10 +1264,10 @@
       </c>
       <c r="J20" s="9" t="n"/>
       <c r="K20" s="10" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="L20" s="10" t="n">
-        <v>3716</v>
+        <v>3689</v>
       </c>
     </row>
     <row r="21">
@@ -1306,10 +1306,10 @@
       </c>
       <c r="J21" s="6" t="n"/>
       <c r="K21" s="7" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="L21" s="7" t="n">
-        <v>3716</v>
+        <v>3689</v>
       </c>
     </row>
     <row r="22">
@@ -1348,10 +1348,10 @@
       </c>
       <c r="J22" s="9" t="n"/>
       <c r="K22" s="10" t="n">
-        <v>7322.2</v>
+        <v>7280</v>
       </c>
       <c r="L22" s="10" t="n">
-        <v>3661</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="23">
@@ -1390,10 +1390,10 @@
       </c>
       <c r="J23" s="6" t="n"/>
       <c r="K23" s="7" t="n">
-        <v>7322.2</v>
+        <v>7280</v>
       </c>
       <c r="L23" s="7" t="n">
-        <v>3661</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="24">
@@ -1432,10 +1432,10 @@
       </c>
       <c r="J24" s="9" t="n"/>
       <c r="K24" s="10" t="n">
-        <v>7322.2</v>
+        <v>7280</v>
       </c>
       <c r="L24" s="10" t="n">
-        <v>3661</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="25">
@@ -1474,10 +1474,10 @@
       </c>
       <c r="J25" s="6" t="n"/>
       <c r="K25" s="7" t="n">
-        <v>7322.2</v>
+        <v>7280</v>
       </c>
       <c r="L25" s="7" t="n">
-        <v>3661</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="26">
@@ -1516,10 +1516,10 @@
       </c>
       <c r="J26" s="9" t="n"/>
       <c r="K26" s="10" t="n">
-        <v>7322.2</v>
+        <v>7280</v>
       </c>
       <c r="L26" s="10" t="n">
-        <v>3661</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="27">
@@ -1558,10 +1558,10 @@
       </c>
       <c r="J27" s="6" t="n"/>
       <c r="K27" s="7" t="n">
-        <v>7322.2</v>
+        <v>7280</v>
       </c>
       <c r="L27" s="7" t="n">
-        <v>3661</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="28">
@@ -1600,10 +1600,10 @@
       </c>
       <c r="J28" s="9" t="n"/>
       <c r="K28" s="10" t="n">
-        <v>7322.2</v>
+        <v>7280</v>
       </c>
       <c r="L28" s="10" t="n">
-        <v>3661</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="29">
@@ -1642,10 +1642,10 @@
       </c>
       <c r="J29" s="6" t="n"/>
       <c r="K29" s="7" t="n">
-        <v>7322.2</v>
+        <v>7280</v>
       </c>
       <c r="L29" s="7" t="n">
-        <v>3661</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="30">
@@ -1684,10 +1684,10 @@
       </c>
       <c r="J30" s="9" t="n"/>
       <c r="K30" s="10" t="n">
-        <v>7322.2</v>
+        <v>7280</v>
       </c>
       <c r="L30" s="10" t="n">
-        <v>3661</v>
+        <v>3640</v>
       </c>
     </row>
     <row r="31">
@@ -1726,10 +1726,10 @@
       </c>
       <c r="J31" s="6" t="n"/>
       <c r="K31" s="7" t="n">
-        <v>7432.03</v>
+        <v>7377.5</v>
       </c>
       <c r="L31" s="7" t="n">
-        <v>3716</v>
+        <v>3689</v>
       </c>
     </row>
     <row r="32">
@@ -1768,10 +1768,10 @@
       </c>
       <c r="J32" s="9" t="n"/>
       <c r="K32" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="L32" s="10" t="n">
-        <v>3772</v>
+        <v>3738</v>
       </c>
     </row>
     <row r="33">
@@ -1810,10 +1810,10 @@
       </c>
       <c r="J33" s="6" t="n"/>
       <c r="K33" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="L33" s="7" t="n">
-        <v>3772</v>
+        <v>3738</v>
       </c>
     </row>
     <row r="34">
@@ -1852,10 +1852,10 @@
       </c>
       <c r="J34" s="9" t="n"/>
       <c r="K34" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="L34" s="10" t="n">
-        <v>3772</v>
+        <v>3738</v>
       </c>
     </row>
     <row r="35">
@@ -1894,10 +1894,10 @@
       </c>
       <c r="J35" s="6" t="n"/>
       <c r="K35" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="L35" s="7" t="n">
-        <v>3772</v>
+        <v>3738</v>
       </c>
     </row>
     <row r="36">
@@ -1936,10 +1936,10 @@
       </c>
       <c r="J36" s="9" t="n"/>
       <c r="K36" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="L36" s="10" t="n">
-        <v>3772</v>
+        <v>3738</v>
       </c>
     </row>
     <row r="37">
@@ -1978,10 +1978,10 @@
       </c>
       <c r="J37" s="6" t="n"/>
       <c r="K37" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="L37" s="7" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
     </row>
     <row r="38">
@@ -2020,10 +2020,10 @@
       </c>
       <c r="J38" s="9" t="n"/>
       <c r="K38" s="10" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="L38" s="10" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
     </row>
     <row r="39">
@@ -2062,10 +2062,10 @@
       </c>
       <c r="J39" s="6" t="n"/>
       <c r="K39" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="L39" s="7" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
     </row>
     <row r="40">
@@ -2104,10 +2104,10 @@
       </c>
       <c r="J40" s="9" t="n"/>
       <c r="K40" s="10" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="L40" s="10" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
     </row>
     <row r="41">
@@ -2146,10 +2146,10 @@
       </c>
       <c r="J41" s="6" t="n"/>
       <c r="K41" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="L41" s="7" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
     </row>
     <row r="42">
@@ -2188,10 +2188,10 @@
       </c>
       <c r="J42" s="9" t="n"/>
       <c r="K42" s="10" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="L42" s="10" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
     </row>
     <row r="43">
@@ -2230,10 +2230,10 @@
       </c>
       <c r="J43" s="6" t="n"/>
       <c r="K43" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="L43" s="7" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
     </row>
     <row r="44">
@@ -2272,10 +2272,10 @@
       </c>
       <c r="J44" s="9" t="n"/>
       <c r="K44" s="10" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="L44" s="10" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
     </row>
     <row r="45">
@@ -2314,10 +2314,10 @@
       </c>
       <c r="J45" s="6" t="n"/>
       <c r="K45" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="L45" s="7" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
     </row>
     <row r="46">
@@ -2356,10 +2356,10 @@
       </c>
       <c r="J46" s="9" t="n"/>
       <c r="K46" s="10" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="L46" s="10" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
     </row>
     <row r="47">
@@ -2398,10 +2398,10 @@
       </c>
       <c r="J47" s="6" t="n"/>
       <c r="K47" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="L47" s="7" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
     </row>
     <row r="48">
@@ -2440,10 +2440,10 @@
       </c>
       <c r="J48" s="9" t="n"/>
       <c r="K48" s="10" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="L48" s="10" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
     </row>
     <row r="49">
@@ -2482,10 +2482,10 @@
       </c>
       <c r="J49" s="6" t="n"/>
       <c r="K49" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="L49" s="7" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
     </row>
     <row r="50">
@@ -2524,10 +2524,10 @@
       </c>
       <c r="J50" s="9" t="n"/>
       <c r="K50" s="10" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="L50" s="10" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
     </row>
     <row r="51">
@@ -2566,10 +2566,10 @@
       </c>
       <c r="J51" s="6" t="n"/>
       <c r="K51" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="L51" s="7" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
     </row>
     <row r="52">
@@ -2608,10 +2608,10 @@
       </c>
       <c r="J52" s="9" t="n"/>
       <c r="K52" s="10" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="L52" s="10" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
     </row>
     <row r="53">
@@ -2650,10 +2650,10 @@
       </c>
       <c r="J53" s="6" t="n"/>
       <c r="K53" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="L53" s="7" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
     </row>
     <row r="54">
@@ -2692,10 +2692,10 @@
       </c>
       <c r="J54" s="9" t="n"/>
       <c r="K54" s="10" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="L54" s="10" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
     </row>
     <row r="55">
@@ -2734,10 +2734,10 @@
       </c>
       <c r="J55" s="6" t="n"/>
       <c r="K55" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="L55" s="7" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
     </row>
     <row r="56">
@@ -2776,10 +2776,10 @@
       </c>
       <c r="J56" s="9" t="n"/>
       <c r="K56" s="10" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="L56" s="10" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
     </row>
     <row r="57">
@@ -2818,10 +2818,10 @@
       </c>
       <c r="J57" s="6" t="n"/>
       <c r="K57" s="7" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="L57" s="7" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
     </row>
     <row r="58">
@@ -2860,10 +2860,10 @@
       </c>
       <c r="J58" s="9" t="n"/>
       <c r="K58" s="10" t="n">
-        <v>7656.67</v>
+        <v>7572.5</v>
       </c>
       <c r="L58" s="10" t="n">
-        <v>3828</v>
+        <v>3786</v>
       </c>
     </row>
     <row r="59">
@@ -2902,10 +2902,10 @@
       </c>
       <c r="J59" s="6" t="n"/>
       <c r="K59" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="L59" s="7" t="n">
-        <v>3772</v>
+        <v>3738</v>
       </c>
     </row>
     <row r="60">
@@ -2944,10 +2944,10 @@
       </c>
       <c r="J60" s="9" t="n"/>
       <c r="K60" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="L60" s="10" t="n">
-        <v>3772</v>
+        <v>3738</v>
       </c>
     </row>
     <row r="61">
@@ -2986,10 +2986,10 @@
       </c>
       <c r="J61" s="6" t="n"/>
       <c r="K61" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="L61" s="7" t="n">
-        <v>3772</v>
+        <v>3738</v>
       </c>
     </row>
     <row r="62">
@@ -3028,10 +3028,10 @@
       </c>
       <c r="J62" s="9" t="n"/>
       <c r="K62" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="L62" s="10" t="n">
-        <v>3772</v>
+        <v>3738</v>
       </c>
     </row>
     <row r="63">
@@ -3070,10 +3070,10 @@
       </c>
       <c r="J63" s="6" t="n"/>
       <c r="K63" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="L63" s="7" t="n">
-        <v>3772</v>
+        <v>3738</v>
       </c>
     </row>
     <row r="64">
@@ -3112,10 +3112,10 @@
       </c>
       <c r="J64" s="9" t="n"/>
       <c r="K64" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="L64" s="10" t="n">
-        <v>3772</v>
+        <v>3738</v>
       </c>
     </row>
     <row r="65">
@@ -3154,10 +3154,10 @@
       </c>
       <c r="J65" s="6" t="n"/>
       <c r="K65" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="L65" s="7" t="n">
-        <v>3772</v>
+        <v>3738</v>
       </c>
     </row>
     <row r="66">
@@ -3196,10 +3196,10 @@
       </c>
       <c r="J66" s="9" t="n"/>
       <c r="K66" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="L66" s="10" t="n">
-        <v>3772</v>
+        <v>3738</v>
       </c>
     </row>
     <row r="67">
@@ -3238,10 +3238,10 @@
       </c>
       <c r="J67" s="6" t="n"/>
       <c r="K67" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="L67" s="7" t="n">
-        <v>3772</v>
+        <v>3738</v>
       </c>
     </row>
     <row r="68">
@@ -3280,10 +3280,10 @@
       </c>
       <c r="J68" s="9" t="n"/>
       <c r="K68" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="L68" s="10" t="n">
-        <v>3772</v>
+        <v>3738</v>
       </c>
     </row>
     <row r="69">
@@ -3322,10 +3322,10 @@
       </c>
       <c r="J69" s="6" t="n"/>
       <c r="K69" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="L69" s="7" t="n">
-        <v>3772</v>
+        <v>3738</v>
       </c>
     </row>
     <row r="70">
@@ -3364,10 +3364,10 @@
       </c>
       <c r="J70" s="9" t="n"/>
       <c r="K70" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="L70" s="10" t="n">
-        <v>3772</v>
+        <v>3738</v>
       </c>
     </row>
     <row r="71">
@@ -3406,10 +3406,10 @@
       </c>
       <c r="J71" s="6" t="n"/>
       <c r="K71" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="L71" s="7" t="n">
-        <v>3772</v>
+        <v>3738</v>
       </c>
     </row>
     <row r="72">
@@ -3448,10 +3448,10 @@
       </c>
       <c r="J72" s="9" t="n"/>
       <c r="K72" s="10" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="L72" s="10" t="n">
-        <v>3772</v>
+        <v>3738</v>
       </c>
     </row>
     <row r="73">
@@ -3490,10 +3490,10 @@
       </c>
       <c r="J73" s="6" t="n"/>
       <c r="K73" s="7" t="n">
-        <v>7543.52</v>
+        <v>7475</v>
       </c>
       <c r="L73" s="7" t="n">
-        <v>3772</v>
+        <v>3738</v>
       </c>
     </row>
     <row r="74">
@@ -3532,10 +3532,10 @@
       </c>
       <c r="J74" s="9" t="n"/>
       <c r="K74" s="10" t="n">
-        <v>7543.52</v>
+        <v>7377.5</v>
       </c>
       <c r="L74" s="10" t="n">
-        <v>3772</v>
+        <v>3689</v>
       </c>
     </row>
     <row r="75">
@@ -3574,10 +3574,10 @@
       </c>
       <c r="J75" s="6" t="n"/>
       <c r="K75" s="7" t="n">
-        <v>7543.52</v>
+        <v>7377.5</v>
       </c>
       <c r="L75" s="7" t="n">
-        <v>3772</v>
+        <v>3689</v>
       </c>
     </row>
     <row r="76">
@@ -3616,10 +3616,10 @@
       </c>
       <c r="J76" s="9" t="n"/>
       <c r="K76" s="10" t="n">
-        <v>7543.52</v>
+        <v>7377.5</v>
       </c>
       <c r="L76" s="10" t="n">
-        <v>3772</v>
+        <v>3689</v>
       </c>
     </row>
     <row r="77">
@@ -3658,10 +3658,10 @@
       </c>
       <c r="J77" s="6" t="n"/>
       <c r="K77" s="7" t="n">
-        <v>7543.52</v>
+        <v>7377.5</v>
       </c>
       <c r="L77" s="7" t="n">
-        <v>3772</v>
+        <v>3689</v>
       </c>
     </row>
     <row r="78">
@@ -3700,10 +3700,10 @@
       </c>
       <c r="J78" s="9" t="n"/>
       <c r="K78" s="10" t="n">
-        <v>7543.52</v>
+        <v>7377.5</v>
       </c>
       <c r="L78" s="10" t="n">
-        <v>3772</v>
+        <v>3689</v>
       </c>
     </row>
   </sheetData>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/09_Surcharge_50pct_1Trip.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/09_Surcharge_50pct_1Trip.xlsx
@@ -518,7 +518,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-05 14:46</t>
+          <t>2026-06-05 16:06</t>
         </is>
       </c>
     </row>
@@ -634,10 +634,10 @@
       </c>
       <c r="J5" s="6" t="n"/>
       <c r="K5" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="L5" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="6">
@@ -676,10 +676,10 @@
       </c>
       <c r="J6" s="9" t="n"/>
       <c r="K6" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="L6" s="10" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="7">
@@ -718,10 +718,10 @@
       </c>
       <c r="J7" s="6" t="n"/>
       <c r="K7" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="8">
@@ -760,10 +760,10 @@
       </c>
       <c r="J8" s="9" t="n"/>
       <c r="K8" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="L8" s="10" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="9">
@@ -802,10 +802,10 @@
       </c>
       <c r="J9" s="6" t="n"/>
       <c r="K9" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="L9" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="10">
@@ -844,10 +844,10 @@
       </c>
       <c r="J10" s="9" t="n"/>
       <c r="K10" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="L10" s="10" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="11">
@@ -886,10 +886,10 @@
       </c>
       <c r="J11" s="6" t="n"/>
       <c r="K11" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="12">
@@ -928,10 +928,10 @@
       </c>
       <c r="J12" s="9" t="n"/>
       <c r="K12" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="L12" s="10" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="13">
@@ -970,10 +970,10 @@
       </c>
       <c r="J13" s="6" t="n"/>
       <c r="K13" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="14">
@@ -1012,10 +1012,10 @@
       </c>
       <c r="J14" s="9" t="n"/>
       <c r="K14" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="L14" s="10" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="15">
@@ -1054,10 +1054,10 @@
       </c>
       <c r="J15" s="6" t="n"/>
       <c r="K15" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="L15" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="16">
@@ -1096,10 +1096,10 @@
       </c>
       <c r="J16" s="9" t="n"/>
       <c r="K16" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="L16" s="10" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="17">
@@ -1138,10 +1138,10 @@
       </c>
       <c r="J17" s="6" t="n"/>
       <c r="K17" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="18">
@@ -1180,10 +1180,10 @@
       </c>
       <c r="J18" s="9" t="n"/>
       <c r="K18" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="L18" s="10" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="19">
@@ -1222,10 +1222,10 @@
       </c>
       <c r="J19" s="6" t="n"/>
       <c r="K19" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="20">
@@ -1264,10 +1264,10 @@
       </c>
       <c r="J20" s="9" t="n"/>
       <c r="K20" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="L20" s="10" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="21">
@@ -1306,10 +1306,10 @@
       </c>
       <c r="J21" s="6" t="n"/>
       <c r="K21" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="L21" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="22">
@@ -1348,10 +1348,10 @@
       </c>
       <c r="J22" s="9" t="n"/>
       <c r="K22" s="10" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="L22" s="10" t="n">
-        <v>3640</v>
+        <v>3584</v>
       </c>
     </row>
     <row r="23">
@@ -1390,10 +1390,10 @@
       </c>
       <c r="J23" s="6" t="n"/>
       <c r="K23" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="L23" s="7" t="n">
-        <v>3640</v>
+        <v>3584</v>
       </c>
     </row>
     <row r="24">
@@ -1432,10 +1432,10 @@
       </c>
       <c r="J24" s="9" t="n"/>
       <c r="K24" s="10" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="L24" s="10" t="n">
-        <v>3640</v>
+        <v>3584</v>
       </c>
     </row>
     <row r="25">
@@ -1474,10 +1474,10 @@
       </c>
       <c r="J25" s="6" t="n"/>
       <c r="K25" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="L25" s="7" t="n">
-        <v>3640</v>
+        <v>3584</v>
       </c>
     </row>
     <row r="26">
@@ -1516,10 +1516,10 @@
       </c>
       <c r="J26" s="9" t="n"/>
       <c r="K26" s="10" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="L26" s="10" t="n">
-        <v>3640</v>
+        <v>3584</v>
       </c>
     </row>
     <row r="27">
@@ -1558,10 +1558,10 @@
       </c>
       <c r="J27" s="6" t="n"/>
       <c r="K27" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="L27" s="7" t="n">
-        <v>3640</v>
+        <v>3584</v>
       </c>
     </row>
     <row r="28">
@@ -1600,10 +1600,10 @@
       </c>
       <c r="J28" s="9" t="n"/>
       <c r="K28" s="10" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="L28" s="10" t="n">
-        <v>3640</v>
+        <v>3584</v>
       </c>
     </row>
     <row r="29">
@@ -1642,10 +1642,10 @@
       </c>
       <c r="J29" s="6" t="n"/>
       <c r="K29" s="7" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="L29" s="7" t="n">
-        <v>3640</v>
+        <v>3584</v>
       </c>
     </row>
     <row r="30">
@@ -1684,10 +1684,10 @@
       </c>
       <c r="J30" s="9" t="n"/>
       <c r="K30" s="10" t="n">
-        <v>7280</v>
+        <v>7168</v>
       </c>
       <c r="L30" s="10" t="n">
-        <v>3640</v>
+        <v>3584</v>
       </c>
     </row>
     <row r="31">
@@ -1726,10 +1726,10 @@
       </c>
       <c r="J31" s="6" t="n"/>
       <c r="K31" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="L31" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="32">
@@ -1768,10 +1768,10 @@
       </c>
       <c r="J32" s="9" t="n"/>
       <c r="K32" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="L32" s="10" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="33">
@@ -1810,10 +1810,10 @@
       </c>
       <c r="J33" s="6" t="n"/>
       <c r="K33" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="L33" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="34">
@@ -1852,10 +1852,10 @@
       </c>
       <c r="J34" s="9" t="n"/>
       <c r="K34" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="L34" s="10" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="35">
@@ -1894,10 +1894,10 @@
       </c>
       <c r="J35" s="6" t="n"/>
       <c r="K35" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="L35" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="36">
@@ -1936,10 +1936,10 @@
       </c>
       <c r="J36" s="9" t="n"/>
       <c r="K36" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="L36" s="10" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="37">
@@ -1978,10 +1978,10 @@
       </c>
       <c r="J37" s="6" t="n"/>
       <c r="K37" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="L37" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="38">
@@ -2020,10 +2020,10 @@
       </c>
       <c r="J38" s="9" t="n"/>
       <c r="K38" s="10" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="L38" s="10" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="39">
@@ -2062,10 +2062,10 @@
       </c>
       <c r="J39" s="6" t="n"/>
       <c r="K39" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="L39" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="40">
@@ -2104,10 +2104,10 @@
       </c>
       <c r="J40" s="9" t="n"/>
       <c r="K40" s="10" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="L40" s="10" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="41">
@@ -2146,10 +2146,10 @@
       </c>
       <c r="J41" s="6" t="n"/>
       <c r="K41" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="L41" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="42">
@@ -2188,10 +2188,10 @@
       </c>
       <c r="J42" s="9" t="n"/>
       <c r="K42" s="10" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="L42" s="10" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="43">
@@ -2230,10 +2230,10 @@
       </c>
       <c r="J43" s="6" t="n"/>
       <c r="K43" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="L43" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="44">
@@ -2272,10 +2272,10 @@
       </c>
       <c r="J44" s="9" t="n"/>
       <c r="K44" s="10" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="L44" s="10" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="45">
@@ -2314,10 +2314,10 @@
       </c>
       <c r="J45" s="6" t="n"/>
       <c r="K45" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="L45" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="46">
@@ -2356,10 +2356,10 @@
       </c>
       <c r="J46" s="9" t="n"/>
       <c r="K46" s="10" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="L46" s="10" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="47">
@@ -2398,10 +2398,10 @@
       </c>
       <c r="J47" s="6" t="n"/>
       <c r="K47" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="L47" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="48">
@@ -2440,10 +2440,10 @@
       </c>
       <c r="J48" s="9" t="n"/>
       <c r="K48" s="10" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="L48" s="10" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="49">
@@ -2482,10 +2482,10 @@
       </c>
       <c r="J49" s="6" t="n"/>
       <c r="K49" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="L49" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="50">
@@ -2524,10 +2524,10 @@
       </c>
       <c r="J50" s="9" t="n"/>
       <c r="K50" s="10" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="L50" s="10" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="51">
@@ -2566,10 +2566,10 @@
       </c>
       <c r="J51" s="6" t="n"/>
       <c r="K51" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="L51" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="52">
@@ -2608,10 +2608,10 @@
       </c>
       <c r="J52" s="9" t="n"/>
       <c r="K52" s="10" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="L52" s="10" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="53">
@@ -2650,10 +2650,10 @@
       </c>
       <c r="J53" s="6" t="n"/>
       <c r="K53" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="L53" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="54">
@@ -2692,10 +2692,10 @@
       </c>
       <c r="J54" s="9" t="n"/>
       <c r="K54" s="10" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="L54" s="10" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="55">
@@ -2734,10 +2734,10 @@
       </c>
       <c r="J55" s="6" t="n"/>
       <c r="K55" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="L55" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="56">
@@ -2776,10 +2776,10 @@
       </c>
       <c r="J56" s="9" t="n"/>
       <c r="K56" s="10" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="L56" s="10" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="57">
@@ -2818,10 +2818,10 @@
       </c>
       <c r="J57" s="6" t="n"/>
       <c r="K57" s="7" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="L57" s="7" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="58">
@@ -2860,10 +2860,10 @@
       </c>
       <c r="J58" s="9" t="n"/>
       <c r="K58" s="10" t="n">
-        <v>7572.5</v>
+        <v>7456</v>
       </c>
       <c r="L58" s="10" t="n">
-        <v>3786</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="59">
@@ -2902,10 +2902,10 @@
       </c>
       <c r="J59" s="6" t="n"/>
       <c r="K59" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="L59" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="60">
@@ -2944,10 +2944,10 @@
       </c>
       <c r="J60" s="9" t="n"/>
       <c r="K60" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="L60" s="10" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="61">
@@ -2986,10 +2986,10 @@
       </c>
       <c r="J61" s="6" t="n"/>
       <c r="K61" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="L61" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="62">
@@ -3028,10 +3028,10 @@
       </c>
       <c r="J62" s="9" t="n"/>
       <c r="K62" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="L62" s="10" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="63">
@@ -3070,10 +3070,10 @@
       </c>
       <c r="J63" s="6" t="n"/>
       <c r="K63" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="L63" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="64">
@@ -3112,10 +3112,10 @@
       </c>
       <c r="J64" s="9" t="n"/>
       <c r="K64" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="L64" s="10" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="65">
@@ -3154,10 +3154,10 @@
       </c>
       <c r="J65" s="6" t="n"/>
       <c r="K65" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="L65" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="66">
@@ -3196,10 +3196,10 @@
       </c>
       <c r="J66" s="9" t="n"/>
       <c r="K66" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="L66" s="10" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="67">
@@ -3238,10 +3238,10 @@
       </c>
       <c r="J67" s="6" t="n"/>
       <c r="K67" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="L67" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="68">
@@ -3280,10 +3280,10 @@
       </c>
       <c r="J68" s="9" t="n"/>
       <c r="K68" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="L68" s="10" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="69">
@@ -3322,10 +3322,10 @@
       </c>
       <c r="J69" s="6" t="n"/>
       <c r="K69" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="L69" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="70">
@@ -3364,10 +3364,10 @@
       </c>
       <c r="J70" s="9" t="n"/>
       <c r="K70" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="L70" s="10" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="71">
@@ -3406,10 +3406,10 @@
       </c>
       <c r="J71" s="6" t="n"/>
       <c r="K71" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="L71" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="72">
@@ -3448,10 +3448,10 @@
       </c>
       <c r="J72" s="9" t="n"/>
       <c r="K72" s="10" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="L72" s="10" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="73">
@@ -3490,10 +3490,10 @@
       </c>
       <c r="J73" s="6" t="n"/>
       <c r="K73" s="7" t="n">
-        <v>7475</v>
+        <v>7360</v>
       </c>
       <c r="L73" s="7" t="n">
-        <v>3738</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="74">
@@ -3532,10 +3532,10 @@
       </c>
       <c r="J74" s="9" t="n"/>
       <c r="K74" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="L74" s="10" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="75">
@@ -3574,10 +3574,10 @@
       </c>
       <c r="J75" s="6" t="n"/>
       <c r="K75" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="L75" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="76">
@@ -3616,10 +3616,10 @@
       </c>
       <c r="J76" s="9" t="n"/>
       <c r="K76" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="L76" s="10" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="77">
@@ -3658,10 +3658,10 @@
       </c>
       <c r="J77" s="6" t="n"/>
       <c r="K77" s="7" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="L77" s="7" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="78">
@@ -3700,10 +3700,10 @@
       </c>
       <c r="J78" s="9" t="n"/>
       <c r="K78" s="10" t="n">
-        <v>7377.5</v>
+        <v>7264</v>
       </c>
       <c r="L78" s="10" t="n">
-        <v>3689</v>
+        <v>3632</v>
       </c>
     </row>
   </sheetData>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/09_Surcharge_50pct_1Trip.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/09_Surcharge_50pct_1Trip.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Surcharge_50pct_1Trip" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Surcharge_50pct_1Trip'!$A$4:$L$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Surcharge_50pct_1Trip'!$A$4:$L$87</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L78"/>
+  <dimension ref="A1:L87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -518,7 +518,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-05 16:06</t>
+          <t>2026-06-05 21:22</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E5" s="6" t="n">
@@ -656,11 +656,11 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>no_finish_day</t>
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
@@ -679,12 +679,12 @@
         <v>7264</v>
       </c>
       <c r="L6" s="10" t="n">
-        <v>3632</v>
+        <v>7264</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n">
-        <v>46145</v>
+        <v>46144</v>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
@@ -698,11 +698,11 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>no_finish_day</t>
         </is>
       </c>
       <c r="E7" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
@@ -721,7 +721,7 @@
         <v>7264</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>3632</v>
+        <v>7264</v>
       </c>
     </row>
     <row r="8">
@@ -740,11 +740,11 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>no_finish_day</t>
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
@@ -763,12 +763,12 @@
         <v>7264</v>
       </c>
       <c r="L8" s="10" t="n">
-        <v>3632</v>
+        <v>7264</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n">
-        <v>46146</v>
+        <v>46144</v>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
@@ -782,7 +782,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E9" s="6" t="n">
@@ -810,7 +810,7 @@
     </row>
     <row r="10">
       <c r="A10" s="8" t="n">
-        <v>46145</v>
+        <v>46144</v>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
@@ -824,11 +824,11 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>no_finish_day</t>
         </is>
       </c>
       <c r="E10" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
@@ -847,26 +847,26 @@
         <v>7264</v>
       </c>
       <c r="L10" s="10" t="n">
-        <v>3632</v>
+        <v>7264</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n">
-        <v>46146</v>
+        <v>46145</v>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E11" s="6" t="n">
@@ -894,11 +894,11 @@
     </row>
     <row r="12">
       <c r="A12" s="8" t="n">
-        <v>46146</v>
+        <v>46145</v>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>72-1218</t>
+          <t>71-6802</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E12" s="9" t="n">
@@ -936,21 +936,21 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n">
-        <v>46146</v>
+        <v>46145</v>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E13" s="6" t="n">
@@ -965,7 +965,7 @@
       <c r="H13" s="6" t="n"/>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="J13" s="6" t="n"/>
@@ -982,17 +982,17 @@
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>71-6802</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E14" s="9" t="n">
@@ -1020,11 +1020,11 @@
     </row>
     <row r="15">
       <c r="A15" s="5" t="n">
-        <v>46147</v>
+        <v>46146</v>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-6802</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E15" s="6" t="n">
@@ -1062,11 +1062,11 @@
     </row>
     <row r="16">
       <c r="A16" s="8" t="n">
-        <v>46147</v>
+        <v>46146</v>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>72-1218</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E16" s="9" t="n">
@@ -1104,11 +1104,11 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="n">
-        <v>46148</v>
+        <v>46146</v>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -1118,7 +1118,7 @@
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E17" s="6" t="n">
@@ -1133,7 +1133,7 @@
       <c r="H17" s="6" t="n"/>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="J17" s="6" t="n"/>
@@ -1146,11 +1146,11 @@
     </row>
     <row r="18">
       <c r="A18" s="8" t="n">
-        <v>46148</v>
+        <v>46147</v>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>72-1218</t>
+          <t>71-6802</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E18" s="9" t="n">
@@ -1202,11 +1202,11 @@
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>no_finish_day</t>
         </is>
       </c>
       <c r="E19" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
@@ -1225,7 +1225,7 @@
         <v>7264</v>
       </c>
       <c r="L19" s="7" t="n">
-        <v>3632</v>
+        <v>7264</v>
       </c>
     </row>
     <row r="20">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E20" s="9" t="n">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>72-1218</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1286,7 +1286,7 @@
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E21" s="6" t="n">
@@ -1314,21 +1314,21 @@
     </row>
     <row r="22">
       <c r="A22" s="8" t="n">
-        <v>46151</v>
+        <v>46149</v>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E22" s="9" t="n">
@@ -1343,15 +1343,15 @@
       <c r="H22" s="9" t="n"/>
       <c r="I22" s="9" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="J22" s="9" t="n"/>
       <c r="K22" s="10" t="n">
-        <v>7168</v>
+        <v>7264</v>
       </c>
       <c r="L22" s="10" t="n">
-        <v>3584</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="23">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E23" s="6" t="n">
@@ -1398,11 +1398,11 @@
     </row>
     <row r="24">
       <c r="A24" s="8" t="n">
-        <v>46152</v>
+        <v>46150</v>
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E24" s="9" t="n">
@@ -1427,7 +1427,7 @@
       <c r="H24" s="9" t="n"/>
       <c r="I24" s="9" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="J24" s="9" t="n"/>
@@ -1440,21 +1440,21 @@
     </row>
     <row r="25">
       <c r="A25" s="5" t="n">
-        <v>46151</v>
+        <v>46150</v>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1218</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E25" s="6" t="n">
@@ -1469,7 +1469,7 @@
       <c r="H25" s="6" t="n"/>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="J25" s="6" t="n"/>
@@ -1482,21 +1482,21 @@
     </row>
     <row r="26">
       <c r="A26" s="8" t="n">
-        <v>46152</v>
+        <v>46151</v>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C26" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E26" s="9" t="n">
@@ -1524,21 +1524,21 @@
     </row>
     <row r="27">
       <c r="A27" s="5" t="n">
-        <v>46151</v>
+        <v>46152</v>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>72-1218</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E27" s="6" t="n">
@@ -1553,7 +1553,7 @@
       <c r="H27" s="6" t="n"/>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="J27" s="6" t="n"/>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>71-5041</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C28" s="9" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E28" s="9" t="n">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E29" s="6" t="n">
@@ -1650,7 +1650,7 @@
     </row>
     <row r="30">
       <c r="A30" s="8" t="n">
-        <v>46154</v>
+        <v>46153</v>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E30" s="9" t="n">
@@ -1679,7 +1679,7 @@
       <c r="H30" s="9" t="n"/>
       <c r="I30" s="9" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="J30" s="9" t="n"/>
@@ -1692,21 +1692,21 @@
     </row>
     <row r="31">
       <c r="A31" s="5" t="n">
-        <v>46155</v>
+        <v>46153</v>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E31" s="6" t="n">
@@ -1721,20 +1721,20 @@
       <c r="H31" s="6" t="n"/>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="J31" s="6" t="n"/>
       <c r="K31" s="7" t="n">
-        <v>7264</v>
+        <v>7168</v>
       </c>
       <c r="L31" s="7" t="n">
-        <v>3632</v>
+        <v>3584</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="n">
-        <v>46157</v>
+        <v>46155</v>
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E32" s="9" t="n">
@@ -1763,20 +1763,20 @@
       <c r="H32" s="9" t="n"/>
       <c r="I32" s="9" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J32" s="9" t="n"/>
       <c r="K32" s="10" t="n">
-        <v>7360</v>
+        <v>7264</v>
       </c>
       <c r="L32" s="10" t="n">
-        <v>3680</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="n">
-        <v>46156</v>
+        <v>46155</v>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E33" s="6" t="n">
@@ -1805,15 +1805,15 @@
       <c r="H33" s="6" t="n"/>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="J33" s="6" t="n"/>
       <c r="K33" s="7" t="n">
-        <v>7360</v>
+        <v>7264</v>
       </c>
       <c r="L33" s="7" t="n">
-        <v>3680</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="34">
@@ -1822,17 +1822,17 @@
       </c>
       <c r="B34" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E34" s="9" t="n">
@@ -1860,21 +1860,21 @@
     </row>
     <row r="35">
       <c r="A35" s="5" t="n">
-        <v>46158</v>
+        <v>46156</v>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E35" s="6" t="n">
@@ -1889,7 +1889,7 @@
       <c r="H35" s="6" t="n"/>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="J35" s="6" t="n"/>
@@ -1902,11 +1902,11 @@
     </row>
     <row r="36">
       <c r="A36" s="8" t="n">
-        <v>46160</v>
+        <v>46157</v>
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-5041</t>
         </is>
       </c>
       <c r="C36" s="9" t="inlineStr">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E36" s="9" t="n">
@@ -1931,7 +1931,7 @@
       <c r="H36" s="9" t="n"/>
       <c r="I36" s="9" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="J36" s="9" t="n"/>
@@ -1944,11 +1944,11 @@
     </row>
     <row r="37">
       <c r="A37" s="5" t="n">
-        <v>46161</v>
+        <v>46157</v>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E37" s="6" t="n">
@@ -1973,34 +1973,34 @@
       <c r="H37" s="6" t="n"/>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="J37" s="6" t="n"/>
       <c r="K37" s="7" t="n">
-        <v>7456</v>
+        <v>7360</v>
       </c>
       <c r="L37" s="7" t="n">
-        <v>3728</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="n">
-        <v>46161</v>
+        <v>46157</v>
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E38" s="9" t="n">
@@ -2015,34 +2015,34 @@
       <c r="H38" s="9" t="n"/>
       <c r="I38" s="9" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="J38" s="9" t="n"/>
       <c r="K38" s="10" t="n">
-        <v>7456</v>
+        <v>7360</v>
       </c>
       <c r="L38" s="10" t="n">
-        <v>3728</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="n">
-        <v>46161</v>
+        <v>46159</v>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E39" s="6" t="n">
@@ -2057,24 +2057,24 @@
       <c r="H39" s="6" t="n"/>
       <c r="I39" s="6" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="J39" s="6" t="n"/>
       <c r="K39" s="7" t="n">
-        <v>7456</v>
+        <v>7360</v>
       </c>
       <c r="L39" s="7" t="n">
-        <v>3728</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="8" t="n">
-        <v>46161</v>
+        <v>46159</v>
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
@@ -2084,11 +2084,11 @@
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>no_finish_day</t>
         </is>
       </c>
       <c r="E40" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F40" s="9" t="inlineStr">
         <is>
@@ -2099,34 +2099,34 @@
       <c r="H40" s="9" t="n"/>
       <c r="I40" s="9" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="J40" s="9" t="n"/>
       <c r="K40" s="10" t="n">
-        <v>7456</v>
+        <v>7360</v>
       </c>
       <c r="L40" s="10" t="n">
-        <v>3728</v>
+        <v>7360</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="n">
-        <v>46161</v>
+        <v>46159</v>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E41" s="6" t="n">
@@ -2141,24 +2141,24 @@
       <c r="H41" s="6" t="n"/>
       <c r="I41" s="6" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-17</t>
         </is>
       </c>
       <c r="J41" s="6" t="n"/>
       <c r="K41" s="7" t="n">
-        <v>7456</v>
+        <v>7360</v>
       </c>
       <c r="L41" s="7" t="n">
-        <v>3728</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="n">
-        <v>46162</v>
+        <v>46160</v>
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C42" s="9" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E42" s="9" t="n">
@@ -2183,24 +2183,24 @@
       <c r="H42" s="9" t="n"/>
       <c r="I42" s="9" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="J42" s="9" t="n"/>
       <c r="K42" s="10" t="n">
-        <v>7456</v>
+        <v>7360</v>
       </c>
       <c r="L42" s="10" t="n">
-        <v>3728</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="n">
-        <v>46162</v>
+        <v>46160</v>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E43" s="6" t="n">
@@ -2225,34 +2225,34 @@
       <c r="H43" s="6" t="n"/>
       <c r="I43" s="6" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="J43" s="6" t="n"/>
       <c r="K43" s="7" t="n">
-        <v>7456</v>
+        <v>7360</v>
       </c>
       <c r="L43" s="7" t="n">
-        <v>3728</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="8" t="n">
-        <v>46162</v>
+        <v>46160</v>
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E44" s="9" t="n">
@@ -2267,24 +2267,24 @@
       <c r="H44" s="9" t="n"/>
       <c r="I44" s="9" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="J44" s="9" t="n"/>
       <c r="K44" s="10" t="n">
-        <v>7456</v>
+        <v>7360</v>
       </c>
       <c r="L44" s="10" t="n">
-        <v>3728</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="n">
-        <v>46163</v>
+        <v>46161</v>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -2294,7 +2294,7 @@
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E45" s="6" t="n">
@@ -2309,7 +2309,7 @@
       <c r="H45" s="6" t="n"/>
       <c r="I45" s="6" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="J45" s="6" t="n"/>
@@ -2322,21 +2322,21 @@
     </row>
     <row r="46">
       <c r="A46" s="8" t="n">
-        <v>46163</v>
+        <v>46161</v>
       </c>
       <c r="B46" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E46" s="9" t="n">
@@ -2351,7 +2351,7 @@
       <c r="H46" s="9" t="n"/>
       <c r="I46" s="9" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="J46" s="9" t="n"/>
@@ -2364,11 +2364,11 @@
     </row>
     <row r="47">
       <c r="A47" s="5" t="n">
-        <v>46163</v>
+        <v>46161</v>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E47" s="6" t="n">
@@ -2393,7 +2393,7 @@
       <c r="H47" s="6" t="n"/>
       <c r="I47" s="6" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="J47" s="6" t="n"/>
@@ -2406,11 +2406,11 @@
     </row>
     <row r="48">
       <c r="A48" s="8" t="n">
-        <v>46164</v>
+        <v>46162</v>
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C48" s="9" t="inlineStr">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E48" s="9" t="n">
@@ -2435,7 +2435,7 @@
       <c r="H48" s="9" t="n"/>
       <c r="I48" s="9" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J48" s="9" t="n"/>
@@ -2448,11 +2448,11 @@
     </row>
     <row r="49">
       <c r="A49" s="5" t="n">
-        <v>46164</v>
+        <v>46162</v>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E49" s="6" t="n">
@@ -2477,7 +2477,7 @@
       <c r="H49" s="6" t="n"/>
       <c r="I49" s="6" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J49" s="6" t="n"/>
@@ -2490,21 +2490,21 @@
     </row>
     <row r="50">
       <c r="A50" s="8" t="n">
-        <v>46164</v>
+        <v>46162</v>
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E50" s="9" t="n">
@@ -2519,7 +2519,7 @@
       <c r="H50" s="9" t="n"/>
       <c r="I50" s="9" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="J50" s="9" t="n"/>
@@ -2532,11 +2532,11 @@
     </row>
     <row r="51">
       <c r="A51" s="5" t="n">
-        <v>46164</v>
+        <v>46163</v>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
@@ -2546,7 +2546,7 @@
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E51" s="6" t="n">
@@ -2561,7 +2561,7 @@
       <c r="H51" s="6" t="n"/>
       <c r="I51" s="6" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="J51" s="6" t="n"/>
@@ -2574,11 +2574,11 @@
     </row>
     <row r="52">
       <c r="A52" s="8" t="n">
-        <v>46165</v>
+        <v>46163</v>
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C52" s="9" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E52" s="9" t="n">
@@ -2603,7 +2603,7 @@
       <c r="H52" s="9" t="n"/>
       <c r="I52" s="9" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="J52" s="9" t="n"/>
@@ -2616,11 +2616,11 @@
     </row>
     <row r="53">
       <c r="A53" s="5" t="n">
-        <v>46165</v>
+        <v>46163</v>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E53" s="6" t="n">
@@ -2645,7 +2645,7 @@
       <c r="H53" s="6" t="n"/>
       <c r="I53" s="6" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="J53" s="6" t="n"/>
@@ -2658,21 +2658,21 @@
     </row>
     <row r="54">
       <c r="A54" s="8" t="n">
-        <v>46166</v>
+        <v>46163</v>
       </c>
       <c r="B54" s="9" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E54" s="9" t="n">
@@ -2687,7 +2687,7 @@
       <c r="H54" s="9" t="n"/>
       <c r="I54" s="9" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="J54" s="9" t="n"/>
@@ -2700,21 +2700,21 @@
     </row>
     <row r="55">
       <c r="A55" s="5" t="n">
-        <v>46165</v>
+        <v>46164</v>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E55" s="6" t="n">
@@ -2729,7 +2729,7 @@
       <c r="H55" s="6" t="n"/>
       <c r="I55" s="6" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="J55" s="6" t="n"/>
@@ -2742,11 +2742,11 @@
     </row>
     <row r="56">
       <c r="A56" s="8" t="n">
-        <v>46166</v>
+        <v>46164</v>
       </c>
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C56" s="9" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E56" s="9" t="n">
@@ -2771,7 +2771,7 @@
       <c r="H56" s="9" t="n"/>
       <c r="I56" s="9" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="J56" s="9" t="n"/>
@@ -2784,7 +2784,7 @@
     </row>
     <row r="57">
       <c r="A57" s="5" t="n">
-        <v>46166</v>
+        <v>46164</v>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
@@ -2798,7 +2798,7 @@
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E57" s="6" t="n">
@@ -2813,7 +2813,7 @@
       <c r="H57" s="6" t="n"/>
       <c r="I57" s="6" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="J57" s="6" t="n"/>
@@ -2826,21 +2826,21 @@
     </row>
     <row r="58">
       <c r="A58" s="8" t="n">
-        <v>46167</v>
+        <v>46164</v>
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C58" s="9" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E58" s="9" t="n">
@@ -2855,7 +2855,7 @@
       <c r="H58" s="9" t="n"/>
       <c r="I58" s="9" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="J58" s="9" t="n"/>
@@ -2868,11 +2868,11 @@
     </row>
     <row r="59">
       <c r="A59" s="5" t="n">
-        <v>46168</v>
+        <v>46165</v>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E59" s="6" t="n">
@@ -2897,34 +2897,34 @@
       <c r="H59" s="6" t="n"/>
       <c r="I59" s="6" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="J59" s="6" t="n"/>
       <c r="K59" s="7" t="n">
-        <v>7360</v>
+        <v>7456</v>
       </c>
       <c r="L59" s="7" t="n">
-        <v>3680</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="8" t="n">
-        <v>46168</v>
+        <v>46165</v>
       </c>
       <c r="B60" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E60" s="9" t="n">
@@ -2939,24 +2939,24 @@
       <c r="H60" s="9" t="n"/>
       <c r="I60" s="9" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="J60" s="9" t="n"/>
       <c r="K60" s="10" t="n">
-        <v>7360</v>
+        <v>7456</v>
       </c>
       <c r="L60" s="10" t="n">
-        <v>3680</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="5" t="n">
-        <v>46169</v>
+        <v>46165</v>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E61" s="6" t="n">
@@ -2981,34 +2981,34 @@
       <c r="H61" s="6" t="n"/>
       <c r="I61" s="6" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="J61" s="6" t="n"/>
       <c r="K61" s="7" t="n">
-        <v>7360</v>
+        <v>7456</v>
       </c>
       <c r="L61" s="7" t="n">
-        <v>3680</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="8" t="n">
-        <v>46169</v>
+        <v>46165</v>
       </c>
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E62" s="9" t="n">
@@ -3023,24 +3023,24 @@
       <c r="H62" s="9" t="n"/>
       <c r="I62" s="9" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-23</t>
         </is>
       </c>
       <c r="J62" s="9" t="n"/>
       <c r="K62" s="10" t="n">
-        <v>7360</v>
+        <v>7456</v>
       </c>
       <c r="L62" s="10" t="n">
-        <v>3680</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="5" t="n">
-        <v>46168</v>
+        <v>46166</v>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>71-8005</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="D63" s="6" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E63" s="6" t="n">
@@ -3065,24 +3065,24 @@
       <c r="H63" s="6" t="n"/>
       <c r="I63" s="6" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="J63" s="6" t="n"/>
       <c r="K63" s="7" t="n">
-        <v>7360</v>
+        <v>7456</v>
       </c>
       <c r="L63" s="7" t="n">
-        <v>3680</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="8" t="n">
-        <v>46168</v>
+        <v>46166</v>
       </c>
       <c r="B64" s="9" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C64" s="9" t="inlineStr">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E64" s="9" t="n">
@@ -3107,34 +3107,34 @@
       <c r="H64" s="9" t="n"/>
       <c r="I64" s="9" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="J64" s="9" t="n"/>
       <c r="K64" s="10" t="n">
-        <v>7360</v>
+        <v>7456</v>
       </c>
       <c r="L64" s="10" t="n">
-        <v>3680</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="n">
-        <v>46168</v>
+        <v>46167</v>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E65" s="6" t="n">
@@ -3149,24 +3149,24 @@
       <c r="H65" s="6" t="n"/>
       <c r="I65" s="6" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="J65" s="6" t="n"/>
       <c r="K65" s="7" t="n">
-        <v>7360</v>
+        <v>7456</v>
       </c>
       <c r="L65" s="7" t="n">
-        <v>3680</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="8" t="n">
-        <v>46170</v>
+        <v>46167</v>
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>71-8001</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C66" s="9" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E66" s="9" t="n">
@@ -3191,24 +3191,24 @@
       <c r="H66" s="9" t="n"/>
       <c r="I66" s="9" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="J66" s="9" t="n"/>
       <c r="K66" s="10" t="n">
-        <v>7360</v>
+        <v>7456</v>
       </c>
       <c r="L66" s="10" t="n">
-        <v>3680</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="n">
-        <v>46170</v>
+        <v>46167</v>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
@@ -3218,7 +3218,7 @@
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E67" s="6" t="n">
@@ -3233,24 +3233,24 @@
       <c r="H67" s="6" t="n"/>
       <c r="I67" s="6" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="J67" s="6" t="n"/>
       <c r="K67" s="7" t="n">
-        <v>7360</v>
+        <v>7456</v>
       </c>
       <c r="L67" s="7" t="n">
-        <v>3680</v>
+        <v>3728</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="8" t="n">
-        <v>46170</v>
+        <v>46168</v>
       </c>
       <c r="B68" s="9" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C68" s="9" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E68" s="9" t="n">
@@ -3275,7 +3275,7 @@
       <c r="H68" s="9" t="n"/>
       <c r="I68" s="9" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="J68" s="9" t="n"/>
@@ -3288,25 +3288,25 @@
     </row>
     <row r="69">
       <c r="A69" s="5" t="n">
-        <v>46169</v>
+        <v>46168</v>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>no_finish_day</t>
         </is>
       </c>
       <c r="E69" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F69" s="6" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
       <c r="H69" s="6" t="n"/>
       <c r="I69" s="6" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="J69" s="6" t="n"/>
@@ -3325,16 +3325,16 @@
         <v>7360</v>
       </c>
       <c r="L69" s="7" t="n">
-        <v>3680</v>
+        <v>7360</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="8" t="n">
-        <v>46170</v>
+        <v>46168</v>
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-8005</t>
         </is>
       </c>
       <c r="C70" s="9" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E70" s="9" t="n">
@@ -3359,7 +3359,7 @@
       <c r="H70" s="9" t="n"/>
       <c r="I70" s="9" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="J70" s="9" t="n"/>
@@ -3372,21 +3372,21 @@
     </row>
     <row r="71">
       <c r="A71" s="5" t="n">
-        <v>46170</v>
+        <v>46168</v>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D71" s="6" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E71" s="6" t="n">
@@ -3401,7 +3401,7 @@
       <c r="H71" s="6" t="n"/>
       <c r="I71" s="6" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="J71" s="6" t="n"/>
@@ -3414,25 +3414,25 @@
     </row>
     <row r="72">
       <c r="A72" s="8" t="n">
-        <v>46171</v>
+        <v>46168</v>
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>no_finish_day</t>
         </is>
       </c>
       <c r="E72" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F72" s="9" t="inlineStr">
         <is>
@@ -3443,7 +3443,7 @@
       <c r="H72" s="9" t="n"/>
       <c r="I72" s="9" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="J72" s="9" t="n"/>
@@ -3451,30 +3451,30 @@
         <v>7360</v>
       </c>
       <c r="L72" s="10" t="n">
-        <v>3680</v>
+        <v>7360</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="n">
-        <v>46171</v>
+        <v>46169</v>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D73" s="6" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>no_finish_day</t>
         </is>
       </c>
       <c r="E73" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F73" s="6" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
       <c r="H73" s="6" t="n"/>
       <c r="I73" s="6" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="J73" s="6" t="n"/>
@@ -3493,16 +3493,16 @@
         <v>7360</v>
       </c>
       <c r="L73" s="7" t="n">
-        <v>3680</v>
+        <v>7360</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="8" t="n">
-        <v>46172</v>
+        <v>46169</v>
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C74" s="9" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E74" s="9" t="n">
@@ -3527,24 +3527,24 @@
       <c r="H74" s="9" t="n"/>
       <c r="I74" s="9" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="J74" s="9" t="n"/>
       <c r="K74" s="10" t="n">
-        <v>7264</v>
+        <v>7360</v>
       </c>
       <c r="L74" s="10" t="n">
-        <v>3632</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="n">
-        <v>46173</v>
+        <v>46169</v>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E75" s="6" t="n">
@@ -3569,34 +3569,34 @@
       <c r="H75" s="6" t="n"/>
       <c r="I75" s="6" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="J75" s="6" t="n"/>
       <c r="K75" s="7" t="n">
-        <v>7264</v>
+        <v>7360</v>
       </c>
       <c r="L75" s="7" t="n">
-        <v>3632</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="8" t="n">
-        <v>46173</v>
+        <v>46169</v>
       </c>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E76" s="9" t="n">
@@ -3611,34 +3611,34 @@
       <c r="H76" s="9" t="n"/>
       <c r="I76" s="9" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="J76" s="9" t="n"/>
       <c r="K76" s="10" t="n">
-        <v>7264</v>
+        <v>7360</v>
       </c>
       <c r="L76" s="10" t="n">
-        <v>3632</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="n">
-        <v>46173</v>
+        <v>46169</v>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E77" s="6" t="n">
@@ -3653,34 +3653,34 @@
       <c r="H77" s="6" t="n"/>
       <c r="I77" s="6" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="J77" s="6" t="n"/>
       <c r="K77" s="7" t="n">
-        <v>7264</v>
+        <v>7360</v>
       </c>
       <c r="L77" s="7" t="n">
-        <v>3632</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="8" t="n">
-        <v>46173</v>
+        <v>46170</v>
       </c>
       <c r="B78" s="9" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-8001</t>
         </is>
       </c>
       <c r="C78" s="9" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t>downtime_origin_day</t>
+          <t>one_trip_billed_day</t>
         </is>
       </c>
       <c r="E78" s="9" t="n">
@@ -3695,19 +3695,397 @@
       <c r="H78" s="9" t="n"/>
       <c r="I78" s="9" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="J78" s="9" t="n"/>
       <c r="K78" s="10" t="n">
+        <v>7360</v>
+      </c>
+      <c r="L78" s="10" t="n">
+        <v>3680</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>one_trip_billed_day</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G79" s="6" t="n"/>
+      <c r="H79" s="6" t="n"/>
+      <c r="I79" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="J79" s="6" t="n"/>
+      <c r="K79" s="7" t="n">
+        <v>7360</v>
+      </c>
+      <c r="L79" s="7" t="n">
+        <v>3680</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="8" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B80" s="9" t="inlineStr">
+        <is>
+          <t>72-1217</t>
+        </is>
+      </c>
+      <c r="C80" s="9" t="inlineStr">
+        <is>
+          <t>LCB</t>
+        </is>
+      </c>
+      <c r="D80" s="9" t="inlineStr">
+        <is>
+          <t>one_trip_billed_day</t>
+        </is>
+      </c>
+      <c r="E80" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F80" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G80" s="9" t="n"/>
+      <c r="H80" s="9" t="n"/>
+      <c r="I80" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="J80" s="9" t="n"/>
+      <c r="K80" s="10" t="n">
+        <v>7360</v>
+      </c>
+      <c r="L80" s="10" t="n">
+        <v>3680</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>72-1217</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>LCB</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>one_trip_billed_day</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="n"/>
+      <c r="H81" s="6" t="n"/>
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="J81" s="6" t="n"/>
+      <c r="K81" s="7" t="n">
+        <v>7360</v>
+      </c>
+      <c r="L81" s="7" t="n">
+        <v>3680</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="8" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B82" s="9" t="inlineStr">
+        <is>
+          <t>71-5042</t>
+        </is>
+      </c>
+      <c r="C82" s="9" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D82" s="9" t="inlineStr">
+        <is>
+          <t>one_trip_billed_day</t>
+        </is>
+      </c>
+      <c r="E82" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F82" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G82" s="9" t="n"/>
+      <c r="H82" s="9" t="n"/>
+      <c r="I82" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="J82" s="9" t="n"/>
+      <c r="K82" s="10" t="n">
         <v>7264</v>
       </c>
-      <c r="L78" s="10" t="n">
+      <c r="L82" s="10" t="n">
         <v>3632</v>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" s="5" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>71-8003</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>one_trip_billed_day</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G83" s="6" t="n"/>
+      <c r="H83" s="6" t="n"/>
+      <c r="I83" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="J83" s="6" t="n"/>
+      <c r="K83" s="7" t="n">
+        <v>7264</v>
+      </c>
+      <c r="L83" s="7" t="n">
+        <v>3632</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="8" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B84" s="9" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D84" s="9" t="inlineStr">
+        <is>
+          <t>one_trip_billed_day</t>
+        </is>
+      </c>
+      <c r="E84" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F84" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G84" s="9" t="n"/>
+      <c r="H84" s="9" t="n"/>
+      <c r="I84" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="J84" s="9" t="n"/>
+      <c r="K84" s="10" t="n">
+        <v>7264</v>
+      </c>
+      <c r="L84" s="10" t="n">
+        <v>3632</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>71-8002</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>one_trip_billed_day</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G85" s="6" t="n"/>
+      <c r="H85" s="6" t="n"/>
+      <c r="I85" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="J85" s="6" t="n"/>
+      <c r="K85" s="7" t="n">
+        <v>7264</v>
+      </c>
+      <c r="L85" s="7" t="n">
+        <v>3632</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="8" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B86" s="9" t="inlineStr">
+        <is>
+          <t>71-8009</t>
+        </is>
+      </c>
+      <c r="C86" s="9" t="inlineStr">
+        <is>
+          <t>BigC</t>
+        </is>
+      </c>
+      <c r="D86" s="9" t="inlineStr">
+        <is>
+          <t>one_trip_billed_day</t>
+        </is>
+      </c>
+      <c r="E86" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F86" s="9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G86" s="9" t="n"/>
+      <c r="H86" s="9" t="n"/>
+      <c r="I86" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="J86" s="9" t="n"/>
+      <c r="K86" s="10" t="n">
+        <v>7264</v>
+      </c>
+      <c r="L86" s="10" t="n">
+        <v>3632</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="n">
+        <v>46173</v>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>72-1217</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>LCB</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>one_trip_billed_day</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="n"/>
+      <c r="H87" s="6" t="n"/>
+      <c r="I87" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="J87" s="6" t="n"/>
+      <c r="K87" s="7" t="n">
+        <v>7264</v>
+      </c>
+      <c r="L87" s="7" t="n">
+        <v>3632</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:L78"/>
+  <autoFilter ref="A4:L87"/>
   <mergeCells count="1">
     <mergeCell ref="A1:L1"/>
   </mergeCells>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/09_Surcharge_50pct_1Trip.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/09_Surcharge_50pct_1Trip.xlsx
@@ -518,7 +518,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-05 21:22</t>
+          <t>2026-06-05 22:49</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/09_Surcharge_50pct_1Trip.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/09_Surcharge_50pct_1Trip.xlsx
@@ -518,7 +518,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-05 22:49</t>
+          <t>2026-06-08 18:37</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/09_Surcharge_50pct_1Trip.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/09_Surcharge_50pct_1Trip.xlsx
@@ -518,7 +518,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08 18:37</t>
+          <t>2026-06-08 18:47</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/09_Surcharge_50pct_1Trip.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/09_Surcharge_50pct_1Trip.xlsx
@@ -518,7 +518,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08 18:47</t>
+          <t>2026-06-08 23:00</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/09_Surcharge_50pct_1Trip.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/09_Surcharge_50pct_1Trip.xlsx
@@ -518,7 +518,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-08 23:00</t>
+          <t>2026-06-09 11:47</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/09_Surcharge_50pct_1Trip.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/09_Surcharge_50pct_1Trip.xlsx
@@ -518,7 +518,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09 11:47</t>
+          <t>2026-06-09 15:05</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/09_Surcharge_50pct_1Trip.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/09_Surcharge_50pct_1Trip.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Surcharge_50pct_1Trip" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Surcharge_50pct_1Trip'!$A$4:$L$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Surcharge_50pct_1Trip'!$A$4:$L$86</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -486,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L87"/>
+  <dimension ref="A1:L86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -518,7 +518,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09 15:05</t>
+          <t>2026-06-10 13:46</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D79" s="6" t="inlineStr">
@@ -3750,7 +3750,7 @@
     </row>
     <row r="80">
       <c r="A80" s="8" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B80" s="9" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
       <c r="H80" s="9" t="n"/>
       <c r="I80" s="9" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="J80" s="9" t="n"/>
@@ -3792,16 +3792,16 @@
     </row>
     <row r="81">
       <c r="A81" s="5" t="n">
-        <v>46171</v>
+        <v>46172</v>
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>72-1217</t>
+          <t>71-5042</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>LCB</t>
+          <t>BigC</t>
         </is>
       </c>
       <c r="D81" s="6" t="inlineStr">
@@ -3821,15 +3821,15 @@
       <c r="H81" s="6" t="n"/>
       <c r="I81" s="6" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="J81" s="6" t="n"/>
       <c r="K81" s="7" t="n">
-        <v>7360</v>
+        <v>7264</v>
       </c>
       <c r="L81" s="7" t="n">
-        <v>3680</v>
+        <v>3632</v>
       </c>
     </row>
     <row r="82">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="B82" s="9" t="inlineStr">
         <is>
-          <t>71-5042</t>
+          <t>71-8003</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>71-8003</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
@@ -3918,11 +3918,11 @@
     </row>
     <row r="84">
       <c r="A84" s="8" t="n">
-        <v>46172</v>
+        <v>46173</v>
       </c>
       <c r="B84" s="9" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>71-8002</t>
         </is>
       </c>
       <c r="C84" s="9" t="inlineStr">
@@ -3947,7 +3947,7 @@
       <c r="H84" s="9" t="n"/>
       <c r="I84" s="9" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="J84" s="9" t="n"/>
@@ -3964,7 +3964,7 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>71-8002</t>
+          <t>71-8009</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
@@ -4006,12 +4006,12 @@
       </c>
       <c r="B86" s="9" t="inlineStr">
         <is>
-          <t>71-8009</t>
+          <t>72-1217</t>
         </is>
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>BigC</t>
+          <t>LCB</t>
         </is>
       </c>
       <c r="D86" s="9" t="inlineStr">
@@ -4042,50 +4042,8 @@
         <v>3632</v>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="5" t="n">
-        <v>46173</v>
-      </c>
-      <c r="B87" s="6" t="inlineStr">
-        <is>
-          <t>72-1217</t>
-        </is>
-      </c>
-      <c r="C87" s="6" t="inlineStr">
-        <is>
-          <t>LCB</t>
-        </is>
-      </c>
-      <c r="D87" s="6" t="inlineStr">
-        <is>
-          <t>one_trip_billed_day</t>
-        </is>
-      </c>
-      <c r="E87" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F87" s="6" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G87" s="6" t="n"/>
-      <c r="H87" s="6" t="n"/>
-      <c r="I87" s="6" t="inlineStr">
-        <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="J87" s="6" t="n"/>
-      <c r="K87" s="7" t="n">
-        <v>7264</v>
-      </c>
-      <c r="L87" s="7" t="n">
-        <v>3632</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:L87"/>
+  <autoFilter ref="A4:L86"/>
   <mergeCells count="1">
     <mergeCell ref="A1:L1"/>
   </mergeCells>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/09_Surcharge_50pct_1Trip.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/09_Surcharge_50pct_1Trip.xlsx
@@ -518,7 +518,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10 13:46</t>
+          <t>2026-06-10 15:59</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/09_Surcharge_50pct_1Trip.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/09_Surcharge_50pct_1Trip.xlsx
@@ -518,7 +518,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10 15:59</t>
+          <t>2026-06-10 17:07</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/09_Surcharge_50pct_1Trip.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/09_Surcharge_50pct_1Trip.xlsx
@@ -518,7 +518,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10 17:07</t>
+          <t>2026-06-10 17:57</t>
         </is>
       </c>
     </row>

--- a/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/09_Surcharge_50pct_1Trip.xlsx
+++ b/Oatside/TransportRateCalculator/reports/oatside-apr2026/exports/09_Surcharge_50pct_1Trip.xlsx
@@ -518,7 +518,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-10 17:57</t>
+          <t>2026-06-10 18:21</t>
         </is>
       </c>
     </row>
